--- a/TestData/Sales_Data Sample.xlsx
+++ b/TestData/Sales_Data Sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyOlap\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C736A03-FB2D-48C3-BBC8-74BA6289FFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74239B2-F04C-40AD-8917-2E625B58D5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="938" xr2:uid="{0926A686-6C16-458D-B759-A471657F5770}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="938" activeTab="1" xr2:uid="{0926A686-6C16-458D-B759-A471657F5770}"/>
   </bookViews>
   <sheets>
     <sheet name="Actual" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15759" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15927" uniqueCount="44">
   <si>
     <t>Version</t>
   </si>
@@ -169,6 +169,12 @@
   </si>
   <si>
     <t>DIRECT_CUST</t>
+  </si>
+  <si>
+    <t>HEADCOUNT</t>
+  </si>
+  <si>
+    <t>SALESDAYS</t>
   </si>
 </sst>
 </file>
@@ -572,10 +578,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC7CFB6-8D2D-48BC-8422-B9E5DAEAAFDA}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:I875"/>
+  <dimension ref="A1:I899"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="18.265625" customWidth="1"/>
@@ -613,7 +619,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -642,7 +648,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -671,7 +677,7 @@
         <v>3061.2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -700,7 +706,7 @@
         <v>9129.3599999999988</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -729,7 +735,7 @@
         <v>52379.759999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -758,7 +764,7 @@
         <v>3884.3999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -787,7 +793,7 @@
         <v>1042.0800000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -816,7 +822,7 @@
         <v>-11181.359999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -845,7 +851,7 @@
         <v>3456</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -874,7 +880,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -903,7 +909,7 @@
         <v>151541.51999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -932,7 +938,7 @@
         <v>65342.16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -961,7 +967,7 @@
         <v>742378.32</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -990,7 +996,7 @@
         <v>118128</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1019,7 +1025,7 @@
         <v>510924.96</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -1048,7 +1054,7 @@
         <v>49367.519999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1077,7 +1083,7 @@
         <v>316351.68</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -1106,7 +1112,7 @@
         <v>26122.560000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -1135,7 +1141,7 @@
         <v>201244.08</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -1164,7 +1170,7 @@
         <v>-136431.35999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -1193,7 +1199,7 @@
         <v>290641.43999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -1222,7 +1228,7 @@
         <v>128144.63999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -1251,7 +1257,7 @@
         <v>450293.51999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -1280,7 +1286,7 @@
         <v>65469.84</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -1309,7 +1315,7 @@
         <v>334264.31999999995</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -1338,7 +1344,7 @@
         <v>38692.799999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1367,7 +1373,7 @@
         <v>704.4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1396,7 +1402,7 @@
         <v>55294.080000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1425,7 +1431,7 @@
         <v>580036.79999999993</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -1454,7 +1460,7 @@
         <v>32149.919999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1483,7 +1489,7 @@
         <v>681916.55999999994</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -1512,7 +1518,7 @@
         <v>83300.639999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1541,7 +1547,7 @@
         <v>587584.79999999993</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1570,7 +1576,7 @@
         <v>244426.32</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -1599,7 +1605,7 @@
         <v>64628.160000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>32</v>
       </c>
@@ -1628,7 +1634,7 @@
         <v>-1152</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -1657,7 +1663,7 @@
         <v>5712</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>32</v>
       </c>
@@ -1686,7 +1692,7 @@
         <v>3076.7999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>32</v>
       </c>
@@ -1715,7 +1721,7 @@
         <v>68074.319999999992</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>32</v>
       </c>
@@ -1744,7 +1750,7 @@
         <v>657185.76</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -1773,7 +1779,7 @@
         <v>116827.44000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1802,7 +1808,7 @@
         <v>4142.6400000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>32</v>
       </c>
@@ -1831,7 +1837,7 @@
         <v>8161.9199999999992</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>32</v>
       </c>
@@ -1860,7 +1866,7 @@
         <v>460.32</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>32</v>
       </c>
@@ -1889,7 +1895,7 @@
         <v>182505.60000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>32</v>
       </c>
@@ -1918,7 +1924,7 @@
         <v>8766.7199999999993</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>32</v>
       </c>
@@ -1947,7 +1953,7 @@
         <v>10823.759999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>32</v>
       </c>
@@ -1976,7 +1982,7 @@
         <v>-13182</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>32</v>
       </c>
@@ -2005,7 +2011,7 @@
         <v>42088.08</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>32</v>
       </c>
@@ -2034,7 +2040,7 @@
         <v>283770.71999999997</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -2063,7 +2069,7 @@
         <v>8184.48</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>32</v>
       </c>
@@ -2092,7 +2098,7 @@
         <v>27492.719999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>32</v>
       </c>
@@ -2121,7 +2127,7 @@
         <v>38991.599999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>32</v>
       </c>
@@ -2150,7 +2156,7 @@
         <v>2762.64</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>32</v>
       </c>
@@ -2179,7 +2185,7 @@
         <v>48029.52</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>32</v>
       </c>
@@ -2208,7 +2214,7 @@
         <v>82956</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>32</v>
       </c>
@@ -2701,7 +2707,7 @@
         <v>130562.63999999998</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>32</v>
       </c>
@@ -2730,7 +2736,7 @@
         <v>41995.68</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>32</v>
       </c>
@@ -2759,7 +2765,7 @@
         <v>2149.1999999999998</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>32</v>
       </c>
@@ -2788,7 +2794,7 @@
         <v>15633.599999999999</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>32</v>
       </c>
@@ -2817,7 +2823,7 @@
         <v>60450</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>32</v>
       </c>
@@ -2846,7 +2852,7 @@
         <v>6930.24</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>32</v>
       </c>
@@ -2875,7 +2881,7 @@
         <v>409067.28</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>32</v>
       </c>
@@ -2904,7 +2910,7 @@
         <v>64455.12</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>32</v>
       </c>
@@ -2933,7 +2939,7 @@
         <v>249534.48</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>32</v>
       </c>
@@ -2962,7 +2968,7 @@
         <v>7346.1599999999989</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>32</v>
       </c>
@@ -2991,7 +2997,7 @@
         <v>435418.8</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>32</v>
       </c>
@@ -3020,7 +3026,7 @@
         <v>4011.3599999999997</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>32</v>
       </c>
@@ -3049,7 +3055,7 @@
         <v>2127.3599999999997</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>32</v>
       </c>
@@ -3078,7 +3084,7 @@
         <v>81121.680000000008</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>32</v>
       </c>
@@ -3107,7 +3113,7 @@
         <v>3292.7999999999997</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>32</v>
       </c>
@@ -3136,7 +3142,7 @@
         <v>813.3599999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>32</v>
       </c>
@@ -3165,7 +3171,7 @@
         <v>6105.8399999999992</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>32</v>
       </c>
@@ -3194,7 +3200,7 @@
         <v>2380099.6800000002</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>32</v>
       </c>
@@ -3223,7 +3229,7 @@
         <v>-67623.839999999997</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>32</v>
       </c>
@@ -3252,7 +3258,7 @@
         <v>1597812</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>32</v>
       </c>
@@ -3281,7 +3287,7 @@
         <v>1375128</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>32</v>
       </c>
@@ -3310,7 +3316,7 @@
         <v>861772.07999999984</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>32</v>
       </c>
@@ -3339,7 +3345,7 @@
         <v>39600.480000000003</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>32</v>
       </c>
@@ -3368,7 +3374,7 @@
         <v>941943.84000000008</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>32</v>
       </c>
@@ -3397,7 +3403,7 @@
         <v>90756.96</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>32</v>
       </c>
@@ -3426,7 +3432,7 @@
         <v>1679539.2</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>32</v>
       </c>
@@ -3455,7 +3461,7 @@
         <v>8677.92</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>32</v>
       </c>
@@ -3484,7 +3490,7 @@
         <v>7231.6</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>32</v>
       </c>
@@ -3513,7 +3519,7 @@
         <v>1797.08</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>32</v>
       </c>
@@ -3542,7 +3548,7 @@
         <v>611.6</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>32</v>
       </c>
@@ -3571,7 +3577,7 @@
         <v>497.8</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>32</v>
       </c>
@@ -3600,7 +3606,7 @@
         <v>1407.3</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>32</v>
       </c>
@@ -3629,7 +3635,7 @@
         <v>2972.64</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>32</v>
       </c>
@@ -3658,7 +3664,7 @@
         <v>917.04</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>32</v>
       </c>
@@ -3687,7 +3693,7 @@
         <v>2009.07</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>32</v>
       </c>
@@ -3716,7 +3722,7 @@
         <v>10119.23</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>32</v>
       </c>
@@ -3745,7 +3751,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>32</v>
       </c>
@@ -3774,7 +3780,7 @@
         <v>3957.2</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>32</v>
       </c>
@@ -3803,7 +3809,7 @@
         <v>7013.79</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>32</v>
       </c>
@@ -3832,7 +3838,7 @@
         <v>10433.459999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>32</v>
       </c>
@@ -3861,7 +3867,7 @@
         <v>6452.83</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>32</v>
       </c>
@@ -3890,7 +3896,7 @@
         <v>35.58</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>32</v>
       </c>
@@ -3919,7 +3925,7 @@
         <v>3504.25</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>32</v>
       </c>
@@ -3948,7 +3954,7 @@
         <v>377.55</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>32</v>
       </c>
@@ -3977,7 +3983,7 @@
         <v>5546.11</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>32</v>
       </c>
@@ -4006,7 +4012,7 @@
         <v>27955.73</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>32</v>
       </c>
@@ -4035,7 +4041,7 @@
         <v>44381.63</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>32</v>
       </c>
@@ -4238,7 +4244,7 @@
         <v>11602.97</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>32</v>
       </c>
@@ -4267,7 +4273,7 @@
         <v>12533.78</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>32</v>
       </c>
@@ -4296,7 +4302,7 @@
         <v>56946.26</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>32</v>
       </c>
@@ -4325,7 +4331,7 @@
         <v>26434.91</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>32</v>
       </c>
@@ -4354,7 +4360,7 @@
         <v>29820.97</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>32</v>
       </c>
@@ -4383,7 +4389,7 @@
         <v>7996.8</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>32</v>
       </c>
@@ -4412,7 +4418,7 @@
         <v>20566.66</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>32</v>
       </c>
@@ -4441,7 +4447,7 @@
         <v>17334.62</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>32</v>
       </c>
@@ -4470,7 +4476,7 @@
         <v>18545.38</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>32</v>
       </c>
@@ -4499,7 +4505,7 @@
         <v>372.4</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>32</v>
       </c>
@@ -4528,7 +4534,7 @@
         <v>553.41999999999996</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>32</v>
       </c>
@@ -4557,7 +4563,7 @@
         <v>412.12</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>32</v>
       </c>
@@ -4586,7 +4592,7 @@
         <v>508.45</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>32</v>
       </c>
@@ -4615,7 +4621,7 @@
         <v>1404.93</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>32</v>
       </c>
@@ -4644,7 +4650,7 @@
         <v>186.7</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>32</v>
       </c>
@@ -4673,7 +4679,7 @@
         <v>715.61</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>32</v>
       </c>
@@ -4702,7 +4708,7 @@
         <v>689.52</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>32</v>
       </c>
@@ -4731,7 +4737,7 @@
         <v>3508.49</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>32</v>
       </c>
@@ -4760,7 +4766,7 @@
         <v>1289.3399999999999</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>32</v>
       </c>
@@ -4789,7 +4795,7 @@
         <v>32018.66</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>32</v>
       </c>
@@ -4818,7 +4824,7 @@
         <v>5704.62</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>32</v>
       </c>
@@ -4847,7 +4853,7 @@
         <v>1884.77</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>32</v>
       </c>
@@ -4876,7 +4882,7 @@
         <v>3621.96</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>32</v>
       </c>
@@ -4905,7 +4911,7 @@
         <v>53.11</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>32</v>
       </c>
@@ -4934,7 +4940,7 @@
         <v>88.65</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>32</v>
       </c>
@@ -4963,7 +4969,7 @@
         <v>352.06</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>32</v>
       </c>
@@ -4992,7 +4998,7 @@
         <v>249.57</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>32</v>
       </c>
@@ -5021,7 +5027,7 @@
         <v>336.11</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>32</v>
       </c>
@@ -5050,7 +5056,7 @@
         <v>257.97000000000003</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>32</v>
       </c>
@@ -5079,7 +5085,7 @@
         <v>922.19</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>32</v>
       </c>
@@ -5108,7 +5114,7 @@
         <v>849.56</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>32</v>
       </c>
@@ -5137,7 +5143,7 @@
         <v>8243.7000000000007</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>32</v>
       </c>
@@ -5166,7 +5172,7 @@
         <v>1215.31</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>32</v>
       </c>
@@ -5195,7 +5201,7 @@
         <v>563.1</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>32</v>
       </c>
@@ -5224,7 +5230,7 @@
         <v>749.65</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>32</v>
       </c>
@@ -5253,7 +5259,7 @@
         <v>61.75</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>32</v>
       </c>
@@ -5282,7 +5288,7 @@
         <v>131.55000000000001</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>32</v>
       </c>
@@ -5311,7 +5317,7 @@
         <v>2875.08</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>32</v>
       </c>
@@ -5340,7 +5346,7 @@
         <v>21.52</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>32</v>
       </c>
@@ -5369,7 +5375,7 @@
         <v>16.559999999999999</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>32</v>
       </c>
@@ -5398,7 +5404,7 @@
         <v>12.24</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>32</v>
       </c>
@@ -5427,7 +5433,7 @@
         <v>69.34</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>32</v>
       </c>
@@ -5456,7 +5462,7 @@
         <v>21.87</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>32</v>
       </c>
@@ -5485,7 +5491,7 @@
         <v>300.51</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>32</v>
       </c>
@@ -5514,7 +5520,7 @@
         <v>165.93</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>32</v>
       </c>
@@ -5543,7 +5549,7 @@
         <v>218.61</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>32</v>
       </c>
@@ -5572,7 +5578,7 @@
         <v>119.78</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>32</v>
       </c>
@@ -5601,7 +5607,7 @@
         <v>743.94</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>32</v>
       </c>
@@ -5630,7 +5636,7 @@
         <v>495.16</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>32</v>
       </c>
@@ -5659,7 +5665,7 @@
         <v>473.9</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>32</v>
       </c>
@@ -5688,7 +5694,7 @@
         <v>456.01</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>32</v>
       </c>
@@ -5717,7 +5723,7 @@
         <v>506.75</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>32</v>
       </c>
@@ -5746,7 +5752,7 @@
         <v>1300.8</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>32</v>
       </c>
@@ -5775,7 +5781,7 @@
         <v>1776.52</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>32</v>
       </c>
@@ -5804,7 +5810,7 @@
         <v>956.33</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>32</v>
       </c>
@@ -5833,7 +5839,7 @@
         <v>3567.74</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>32</v>
       </c>
@@ -5862,7 +5868,7 @@
         <v>3390.63</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>32</v>
       </c>
@@ -5891,7 +5897,7 @@
         <v>1295.79</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>32</v>
       </c>
@@ -5920,7 +5926,7 @@
         <v>1090.72</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>32</v>
       </c>
@@ -5949,7 +5955,7 @@
         <v>8296.44</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>32</v>
       </c>
@@ -5978,7 +5984,7 @@
         <v>1928.57</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>32</v>
       </c>
@@ -6007,7 +6013,7 @@
         <v>3019.93</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>32</v>
       </c>
@@ -6036,7 +6042,7 @@
         <v>932.33</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>32</v>
       </c>
@@ -6065,7 +6071,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>32</v>
       </c>
@@ -6094,7 +6100,7 @@
         <v>2079.56</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>32</v>
       </c>
@@ -6123,7 +6129,7 @@
         <v>1451.23</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>32</v>
       </c>
@@ -6152,7 +6158,7 @@
         <v>1923.86</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>32</v>
       </c>
@@ -6181,7 +6187,7 @@
         <v>1298.48</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>32</v>
       </c>
@@ -6210,7 +6216,7 @@
         <v>1805.29</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>32</v>
       </c>
@@ -6239,7 +6245,7 @@
         <v>2800.12</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>32</v>
       </c>
@@ -6268,7 +6274,7 @@
         <v>2057.14</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>32</v>
       </c>
@@ -6297,7 +6303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>32</v>
       </c>
@@ -6326,7 +6332,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>32</v>
       </c>
@@ -6355,7 +6361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>32</v>
       </c>
@@ -6384,7 +6390,7 @@
         <v>494.5</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>32</v>
       </c>
@@ -6413,7 +6419,7 @@
         <v>124.78</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>32</v>
       </c>
@@ -6442,7 +6448,7 @@
         <v>2225.7199999999998</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>32</v>
       </c>
@@ -6471,7 +6477,7 @@
         <v>4824.16</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>32</v>
       </c>
@@ -6500,7 +6506,7 @@
         <v>13786.78</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>32</v>
       </c>
@@ -6529,7 +6535,7 @@
         <v>3157.09</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>32</v>
       </c>
@@ -6558,7 +6564,7 @@
         <v>8227.85</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>32</v>
       </c>
@@ -6587,7 +6593,7 @@
         <v>12485.01</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>32</v>
       </c>
@@ -6616,7 +6622,7 @@
         <v>3199.62</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>32</v>
       </c>
@@ -6645,7 +6651,7 @@
         <v>18576.23</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>32</v>
       </c>
@@ -6674,7 +6680,7 @@
         <v>18499.47</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>32</v>
       </c>
@@ -6703,7 +6709,7 @@
         <v>14315.19</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>32</v>
       </c>
@@ -6732,7 +6738,7 @@
         <v>22254.61</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>32</v>
       </c>
@@ -6761,7 +6767,7 @@
         <v>32764.84</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>32</v>
       </c>
@@ -6790,7 +6796,7 @@
         <v>39497.660000000003</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>32</v>
       </c>
@@ -6819,7 +6825,7 @@
         <v>24849</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>32</v>
       </c>
@@ -6848,7 +6854,7 @@
         <v>752.56</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>32</v>
       </c>
@@ -6877,7 +6883,7 @@
         <v>1992.36</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>32</v>
       </c>
@@ -6906,7 +6912,7 @@
         <v>6642.61</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>32</v>
       </c>
@@ -6935,7 +6941,7 @@
         <v>2008.81</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>32</v>
       </c>
@@ -6964,7 +6970,7 @@
         <v>4671.8500000000004</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>32</v>
       </c>
@@ -6993,7 +6999,7 @@
         <v>4978.8500000000004</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>32</v>
       </c>
@@ -7022,7 +7028,7 @@
         <v>-215.7</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>32</v>
       </c>
@@ -7051,7 +7057,7 @@
         <v>100.01</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>32</v>
       </c>
@@ -7080,7 +7086,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>32</v>
       </c>
@@ -7109,7 +7115,7 @@
         <v>375.3</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>32</v>
       </c>
@@ -7138,7 +7144,7 @@
         <v>174.5</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>32</v>
       </c>
@@ -7167,7 +7173,7 @@
         <v>2537.91</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>32</v>
       </c>
@@ -7196,7 +7202,7 @@
         <v>3716.11</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>32</v>
       </c>
@@ -7225,7 +7231,7 @@
         <v>2446.75</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>32</v>
       </c>
@@ -7254,7 +7260,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>32</v>
       </c>
@@ -7283,7 +7289,7 @@
         <v>172.7</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>32</v>
       </c>
@@ -7312,7 +7318,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>32</v>
       </c>
@@ -7341,7 +7347,7 @@
         <v>491.8</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>32</v>
       </c>
@@ -7370,7 +7376,7 @@
         <v>5092.55</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>32</v>
       </c>
@@ -7399,7 +7405,7 @@
         <v>7163.68</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>32</v>
       </c>
@@ -7428,7 +7434,7 @@
         <v>15019</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>32</v>
       </c>
@@ -7457,7 +7463,7 @@
         <v>11206.93</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>32</v>
       </c>
@@ -7486,7 +7492,7 @@
         <v>4693.9399999999996</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>32</v>
       </c>
@@ -7515,7 +7521,7 @@
         <v>8200.84</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>32</v>
       </c>
@@ -7544,7 +7550,7 @@
         <v>795.98</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>32</v>
       </c>
@@ -7573,7 +7579,7 @@
         <v>2032.14</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>32</v>
       </c>
@@ -7602,7 +7608,7 @@
         <v>2506.65</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>32</v>
       </c>
@@ -7631,7 +7637,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>32</v>
       </c>
@@ -7660,7 +7666,7 @@
         <v>784.8</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>32</v>
       </c>
@@ -7689,7 +7695,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>32</v>
       </c>
@@ -7718,7 +7724,7 @@
         <v>783.56</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>32</v>
       </c>
@@ -7747,7 +7753,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>32</v>
       </c>
@@ -7776,7 +7782,7 @@
         <v>6374.15</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>32</v>
       </c>
@@ -7805,7 +7811,7 @@
         <v>58184.42</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>32</v>
       </c>
@@ -7834,7 +7840,7 @@
         <v>12576.06</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>32</v>
       </c>
@@ -7863,7 +7869,7 @@
         <v>87782.92</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>32</v>
       </c>
@@ -7892,7 +7898,7 @@
         <v>126180.62</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>32</v>
       </c>
@@ -7921,7 +7927,7 @@
         <v>15304.94</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>32</v>
       </c>
@@ -7950,7 +7956,7 @@
         <v>-40.1</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>32</v>
       </c>
@@ -7979,7 +7985,7 @@
         <v>89.55</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>32</v>
       </c>
@@ -8008,7 +8014,7 @@
         <v>191.69</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>32</v>
       </c>
@@ -8037,7 +8043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>32</v>
       </c>
@@ -8066,7 +8072,7 @@
         <v>1780.32</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>32</v>
       </c>
@@ -8095,7 +8101,7 @@
         <v>21256.41</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>32</v>
       </c>
@@ -8124,7 +8130,7 @@
         <v>123002.4</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>32</v>
       </c>
@@ -8153,7 +8159,7 @@
         <v>158147.65</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>32</v>
       </c>
@@ -8182,7 +8188,7 @@
         <v>95531.11</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>32</v>
       </c>
@@ -8211,7 +8217,7 @@
         <v>121253.71</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>32</v>
       </c>
@@ -8240,7 +8246,7 @@
         <v>340.14</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>32</v>
       </c>
@@ -8269,7 +8275,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>32</v>
       </c>
@@ -8298,7 +8304,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>32</v>
       </c>
@@ -8327,7 +8333,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>32</v>
       </c>
@@ -8356,7 +8362,7 @@
         <v>837.26</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>32</v>
       </c>
@@ -8385,7 +8391,7 @@
         <v>836.9</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>32</v>
       </c>
@@ -8414,7 +8420,7 @@
         <v>3792</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>32</v>
       </c>
@@ -8443,7 +8449,7 @@
         <v>4788</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>32</v>
       </c>
@@ -8472,7 +8478,7 @@
         <v>5762.7</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>32</v>
       </c>
@@ -8501,7 +8507,7 @@
         <v>23246.1</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>32</v>
       </c>
@@ -8530,7 +8536,7 @@
         <v>2403.9</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>32</v>
       </c>
@@ -8559,7 +8565,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>32</v>
       </c>
@@ -8588,7 +8594,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>32</v>
       </c>
@@ -8617,7 +8623,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>32</v>
       </c>
@@ -8646,7 +8652,7 @@
         <v>20307.150000000001</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>32</v>
       </c>
@@ -8675,7 +8681,7 @@
         <v>30879.33</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>32</v>
       </c>
@@ -8704,7 +8710,7 @@
         <v>11382.97</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>32</v>
       </c>
@@ -8733,7 +8739,7 @@
         <v>7865.95</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>32</v>
       </c>
@@ -8762,7 +8768,7 @@
         <v>8402.34</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>32</v>
       </c>
@@ -8791,7 +8797,7 @@
         <v>6772.95</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>32</v>
       </c>
@@ -8820,7 +8826,7 @@
         <v>8827.89</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>32</v>
       </c>
@@ -8849,7 +8855,7 @@
         <v>4620.78</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>32</v>
       </c>
@@ -8878,7 +8884,7 @@
         <v>13625.77</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>32</v>
       </c>
@@ -8907,7 +8913,7 @@
         <v>47109.09</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>32</v>
       </c>
@@ -8936,7 +8942,7 @@
         <v>53345.46</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>32</v>
       </c>
@@ -8965,7 +8971,7 @@
         <v>72630.12</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>32</v>
       </c>
@@ -8994,7 +9000,7 @@
         <v>109577.84</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>32</v>
       </c>
@@ -9023,7 +9029,7 @@
         <v>151187.9</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>32</v>
       </c>
@@ -9052,7 +9058,7 @@
         <v>80412.53</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>32</v>
       </c>
@@ -9081,7 +9087,7 @@
         <v>63535.53</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>32</v>
       </c>
@@ -9110,7 +9116,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>32</v>
       </c>
@@ -9139,7 +9145,7 @@
         <v>376.24</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>32</v>
       </c>
@@ -9168,7 +9174,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>32</v>
       </c>
@@ -9197,7 +9203,7 @@
         <v>581.28</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>32</v>
       </c>
@@ -9226,7 +9232,7 @@
         <v>26627</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>32</v>
       </c>
@@ -9255,7 +9261,7 @@
         <v>176.87</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>32</v>
       </c>
@@ -9284,7 +9290,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>32</v>
       </c>
@@ -9313,7 +9319,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>32</v>
       </c>
@@ -9342,7 +9348,7 @@
         <v>10177</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>32</v>
       </c>
@@ -9371,7 +9377,7 @@
         <v>10583.3</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>32</v>
       </c>
@@ -9400,7 +9406,7 @@
         <v>522.5</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>32</v>
       </c>
@@ -9429,7 +9435,7 @@
         <v>839.53</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>32</v>
       </c>
@@ -9458,7 +9464,7 @@
         <v>5778.22</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>32</v>
       </c>
@@ -9487,7 +9493,7 @@
         <v>14648.89</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>32</v>
       </c>
@@ -9516,7 +9522,7 @@
         <v>4476.24</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>32</v>
       </c>
@@ -9545,7 +9551,7 @@
         <v>10842.81</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>32</v>
       </c>
@@ -9574,7 +9580,7 @@
         <v>3592.94</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>32</v>
       </c>
@@ -9603,7 +9609,7 @@
         <v>691.62</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>32</v>
       </c>
@@ -9632,7 +9638,7 @@
         <v>575.54999999999995</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>32</v>
       </c>
@@ -9661,7 +9667,7 @@
         <v>434.13</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>32</v>
       </c>
@@ -9690,7 +9696,7 @@
         <v>1267.32</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>32</v>
       </c>
@@ -9719,7 +9725,7 @@
         <v>1469.7</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>32</v>
       </c>
@@ -9748,7 +9754,7 @@
         <v>245.71</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>32</v>
       </c>
@@ -9777,7 +9783,7 @@
         <v>12228.78</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>32</v>
       </c>
@@ -9806,7 +9812,7 @@
         <v>188.95</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>32</v>
       </c>
@@ -9835,7 +9841,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>32</v>
       </c>
@@ -9864,7 +9870,7 @@
         <v>45313.52</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>32</v>
       </c>
@@ -9893,7 +9899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>32</v>
       </c>
@@ -9922,7 +9928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>32</v>
       </c>
@@ -9951,7 +9957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>32</v>
       </c>
@@ -9980,7 +9986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>32</v>
       </c>
@@ -10009,7 +10015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>32</v>
       </c>
@@ -10038,7 +10044,7 @@
         <v>166.05</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>32</v>
       </c>
@@ -10067,7 +10073,7 @@
         <v>564.69000000000005</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>32</v>
       </c>
@@ -10096,7 +10102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>32</v>
       </c>
@@ -10125,7 +10131,7 @@
         <v>-99.8</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>32</v>
       </c>
@@ -10154,7 +10160,7 @@
         <v>-176.51</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>32</v>
       </c>
@@ -10183,7 +10189,7 @@
         <v>6599.96</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>32</v>
       </c>
@@ -10212,7 +10218,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>32</v>
       </c>
@@ -10241,7 +10247,7 @@
         <v>59.54</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>32</v>
       </c>
@@ -10270,7 +10276,7 @@
         <v>-111.92</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>32</v>
       </c>
@@ -10299,7 +10305,7 @@
         <v>2470.1799999999998</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>32</v>
       </c>
@@ -10328,7 +10334,7 @@
         <v>163.36000000000001</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>32</v>
       </c>
@@ -10357,7 +10363,7 @@
         <v>2117.14</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>32</v>
       </c>
@@ -10386,7 +10392,7 @@
         <v>-135</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>32</v>
       </c>
@@ -10415,7 +10421,7 @@
         <v>1276.25</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>32</v>
       </c>
@@ -10444,7 +10450,7 @@
         <v>2025.06</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>32</v>
       </c>
@@ -10473,7 +10479,7 @@
         <v>91.86</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>32</v>
       </c>
@@ -10502,7 +10508,7 @@
         <v>5337.27</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>32</v>
       </c>
@@ -10531,7 +10537,7 @@
         <v>1521.44</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>32</v>
       </c>
@@ -10560,7 +10566,7 @@
         <v>2721.41</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>32</v>
       </c>
@@ -10589,7 +10595,7 @@
         <v>6575.33</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>32</v>
       </c>
@@ -10618,7 +10624,7 @@
         <v>11247.63</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>32</v>
       </c>
@@ -10647,7 +10653,7 @@
         <v>13240.13</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>32</v>
       </c>
@@ -10676,7 +10682,7 @@
         <v>7592.48</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>32</v>
       </c>
@@ -10705,7 +10711,7 @@
         <v>9969.8700000000008</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>32</v>
       </c>
@@ -10734,7 +10740,7 @@
         <v>20408.09</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>32</v>
       </c>
@@ -10763,7 +10769,7 @@
         <v>6474.63</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>32</v>
       </c>
@@ -10792,7 +10798,7 @@
         <v>3444.74</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>32</v>
       </c>
@@ -10821,7 +10827,7 @@
         <v>7580.47</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>32</v>
       </c>
@@ -10850,7 +10856,7 @@
         <v>2459.34</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>32</v>
       </c>
@@ -10879,7 +10885,7 @@
         <v>7440.34</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>32</v>
       </c>
@@ -10908,7 +10914,7 @@
         <v>10403.24</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>32</v>
       </c>
@@ -10937,7 +10943,7 @@
         <v>3017.67</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>32</v>
       </c>
@@ -10966,7 +10972,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>32</v>
       </c>
@@ -10995,7 +11001,7 @@
         <v>429.5</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>32</v>
       </c>
@@ -11024,7 +11030,7 @@
         <v>581.6</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>32</v>
       </c>
@@ -11053,7 +11059,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>32</v>
       </c>
@@ -11082,7 +11088,7 @@
         <v>1458.58</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>32</v>
       </c>
@@ -11111,7 +11117,7 @@
         <v>4425.49</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>32</v>
       </c>
@@ -11140,7 +11146,7 @@
         <v>1531.37</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>32</v>
       </c>
@@ -11169,7 +11175,7 @@
         <v>2421.25</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>32</v>
       </c>
@@ -11198,7 +11204,7 @@
         <v>1110.26</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>32</v>
       </c>
@@ -11227,7 +11233,7 @@
         <v>5064.51</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>32</v>
       </c>
@@ -11256,7 +11262,7 @@
         <v>473.75</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>32</v>
       </c>
@@ -11285,7 +11291,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>32</v>
       </c>
@@ -11314,7 +11320,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>32</v>
       </c>
@@ -11343,7 +11349,7 @@
         <v>399.46</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>32</v>
       </c>
@@ -11372,7 +11378,7 @@
         <v>264.82</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>32</v>
       </c>
@@ -11401,7 +11407,7 @@
         <v>26853.02</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>32</v>
       </c>
@@ -11430,7 +11436,7 @@
         <v>17377.419999999998</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>32</v>
       </c>
@@ -11459,7 +11465,7 @@
         <v>23004.81</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>32</v>
       </c>
@@ -11488,7 +11494,7 @@
         <v>24517.759999999998</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>32</v>
       </c>
@@ -11517,7 +11523,7 @@
         <v>36638.589999999997</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>32</v>
       </c>
@@ -11546,7 +11552,7 @@
         <v>15004.3</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>32</v>
       </c>
@@ -11575,7 +11581,7 @@
         <v>32635.24</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>32</v>
       </c>
@@ -11604,7 +11610,7 @@
         <v>6593.78</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>32</v>
       </c>
@@ -11633,7 +11639,7 @@
         <v>4628.83</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>32</v>
       </c>
@@ -11662,7 +11668,7 @@
         <v>2398.91</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>32</v>
       </c>
@@ -11691,7 +11697,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>32</v>
       </c>
@@ -11720,7 +11726,7 @@
         <v>2564.85</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>32</v>
       </c>
@@ -11749,7 +11755,7 @@
         <v>6914.2</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>32</v>
       </c>
@@ -11778,7 +11784,7 @@
         <v>8062.8</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>32</v>
       </c>
@@ -11807,7 +11813,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>32</v>
       </c>
@@ -11836,7 +11842,7 @@
         <v>64.2</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>32</v>
       </c>
@@ -11865,7 +11871,7 @@
         <v>599.52</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>32</v>
       </c>
@@ -11894,7 +11900,7 @@
         <v>302.95999999999998</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>32</v>
       </c>
@@ -11923,7 +11929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>32</v>
       </c>
@@ -11952,7 +11958,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>32</v>
       </c>
@@ -11981,7 +11987,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>32</v>
       </c>
@@ -12010,7 +12016,7 @@
         <v>525.67999999999995</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>32</v>
       </c>
@@ -12039,7 +12045,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>32</v>
       </c>
@@ -12068,7 +12074,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>32</v>
       </c>
@@ -12097,7 +12103,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>32</v>
       </c>
@@ -12126,7 +12132,7 @@
         <v>655.5</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>32</v>
       </c>
@@ -12155,7 +12161,7 @@
         <v>631.75</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>32</v>
       </c>
@@ -12184,7 +12190,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>32</v>
       </c>
@@ -12213,7 +12219,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>32</v>
       </c>
@@ -12242,7 +12248,7 @@
         <v>948.23</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>32</v>
       </c>
@@ -12271,7 +12277,7 @@
         <v>71.45</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>32</v>
       </c>
@@ -12300,7 +12306,7 @@
         <v>1248.24</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>32</v>
       </c>
@@ -12329,7 +12335,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>32</v>
       </c>
@@ -12358,7 +12364,7 @@
         <v>-1831.22</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>32</v>
       </c>
@@ -12387,7 +12393,7 @@
         <v>5728.05</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>32</v>
       </c>
@@ -12416,7 +12422,7 @@
         <v>2463.69</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>32</v>
       </c>
@@ -12445,7 +12451,7 @@
         <v>23064.75</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>32</v>
       </c>
@@ -12474,7 +12480,7 @@
         <v>15423.5</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>32</v>
       </c>
@@ -12503,7 +12509,7 @@
         <v>87161.3</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>32</v>
       </c>
@@ -12532,7 +12538,7 @@
         <v>827297.77</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>32</v>
       </c>
@@ -12561,7 +12567,7 @@
         <v>703937.8</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>32</v>
       </c>
@@ -12590,7 +12596,7 @@
         <v>349418.17</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>32</v>
       </c>
@@ -12619,7 +12625,7 @@
         <v>1124158.01</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>32</v>
       </c>
@@ -12648,7 +12654,7 @@
         <v>141.83000000000001</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>32</v>
       </c>
@@ -12677,7 +12683,7 @@
         <v>159.54</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>32</v>
       </c>
@@ -12706,7 +12712,7 @@
         <v>1732.71</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>32</v>
       </c>
@@ -12735,7 +12741,7 @@
         <v>-91.44</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>32</v>
       </c>
@@ -12764,7 +12770,7 @@
         <v>3228.18</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>32</v>
       </c>
@@ -12793,7 +12799,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>32</v>
       </c>
@@ -12822,7 +12828,7 @@
         <v>380.55</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>32</v>
       </c>
@@ -12851,7 +12857,7 @@
         <v>13579.37</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>32</v>
       </c>
@@ -12880,7 +12886,7 @@
         <v>47990.21</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>32</v>
       </c>
@@ -12909,7 +12915,7 @@
         <v>447.66</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>32</v>
       </c>
@@ -12938,7 +12944,7 @@
         <v>7707.41</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>32</v>
       </c>
@@ -12967,7 +12973,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>32</v>
       </c>
@@ -12996,7 +13002,7 @@
         <v>82741.820000000007</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>32</v>
       </c>
@@ -13025,7 +13031,7 @@
         <v>11942.27</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>32</v>
       </c>
@@ -13054,7 +13060,7 @@
         <v>9503.49</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>32</v>
       </c>
@@ -13083,7 +13089,7 @@
         <v>53396.45</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>32</v>
       </c>
@@ -13112,7 +13118,7 @@
         <v>41116.26</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>32</v>
       </c>
@@ -13141,7 +13147,7 @@
         <v>13499.27</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>32</v>
       </c>
@@ -13170,7 +13176,7 @@
         <v>38528.82</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>32</v>
       </c>
@@ -13199,7 +13205,7 @@
         <v>587.4</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>32</v>
       </c>
@@ -13228,7 +13234,7 @@
         <v>464.56</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>32</v>
       </c>
@@ -13257,7 +13263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>32</v>
       </c>
@@ -13286,7 +13292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>32</v>
       </c>
@@ -13315,7 +13321,7 @@
         <v>29.91</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>32</v>
       </c>
@@ -13344,7 +13350,7 @@
         <v>3963.16</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>32</v>
       </c>
@@ -13373,7 +13379,7 @@
         <v>25.74</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>32</v>
       </c>
@@ -13402,7 +13408,7 @@
         <v>5280.6</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>32</v>
       </c>
@@ -13431,7 +13437,7 @@
         <v>121.26</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>32</v>
       </c>
@@ -13460,7 +13466,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>32</v>
       </c>
@@ -13489,7 +13495,7 @@
         <v>-32.85</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>32</v>
       </c>
@@ -13518,7 +13524,7 @@
         <v>3151.16</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>32</v>
       </c>
@@ -13547,7 +13553,7 @@
         <v>3105.14</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>32</v>
       </c>
@@ -13576,7 +13582,7 @@
         <v>2183.9699999999998</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>32</v>
       </c>
@@ -13605,7 +13611,7 @@
         <v>1499.72</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>32</v>
       </c>
@@ -13634,7 +13640,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>32</v>
       </c>
@@ -13663,7 +13669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>32</v>
       </c>
@@ -13692,7 +13698,7 @@
         <v>6736.37</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>32</v>
       </c>
@@ -13721,7 +13727,7 @@
         <v>2463.25</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>32</v>
       </c>
@@ -13750,7 +13756,7 @@
         <v>4974.6899999999996</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>32</v>
       </c>
@@ -13779,7 +13785,7 @@
         <v>3249.61</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>32</v>
       </c>
@@ -13808,7 +13814,7 @@
         <v>8176.43</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>32</v>
       </c>
@@ -13837,7 +13843,7 @@
         <v>1341.42</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>32</v>
       </c>
@@ -13866,7 +13872,7 @@
         <v>6872.61</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>32</v>
       </c>
@@ -13895,7 +13901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>32</v>
       </c>
@@ -13924,7 +13930,7 @@
         <v>-127.5</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>32</v>
       </c>
@@ -13953,7 +13959,7 @@
         <v>1886.49</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>32</v>
       </c>
@@ -13982,7 +13988,7 @@
         <v>69.819999999999993</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>32</v>
       </c>
@@ -14011,7 +14017,7 @@
         <v>325.52</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>32</v>
       </c>
@@ -14040,7 +14046,7 @@
         <v>86.96</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>32</v>
       </c>
@@ -14069,7 +14075,7 @@
         <v>150.77000000000001</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>32</v>
       </c>
@@ -14098,7 +14104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>32</v>
       </c>
@@ -14127,7 +14133,7 @@
         <v>-1662.34</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>32</v>
       </c>
@@ -14156,7 +14162,7 @@
         <v>5416.36</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>32</v>
       </c>
@@ -14185,7 +14191,7 @@
         <v>14613.61</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>32</v>
       </c>
@@ -14214,7 +14220,7 @@
         <v>3978.99</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>32</v>
       </c>
@@ -14243,7 +14249,7 @@
         <v>5537.35</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>32</v>
       </c>
@@ -14272,7 +14278,7 @@
         <v>3739.25</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>32</v>
       </c>
@@ -14301,7 +14307,7 @@
         <v>1531.01</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
         <v>32</v>
       </c>
@@ -14330,7 +14336,7 @@
         <v>2386.73</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
         <v>32</v>
       </c>
@@ -14359,7 +14365,7 @@
         <v>3578.27</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
         <v>32</v>
       </c>
@@ -14388,7 +14394,7 @@
         <v>2312.27</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
         <v>32</v>
       </c>
@@ -14417,7 +14423,7 @@
         <v>3857.23</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
         <v>32</v>
       </c>
@@ -14446,7 +14452,7 @@
         <v>2325.1799999999998</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>32</v>
       </c>
@@ -14475,7 +14481,7 @@
         <v>18416.71</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
         <v>32</v>
       </c>
@@ -14504,7 +14510,7 @@
         <v>11118.54</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
         <v>32</v>
       </c>
@@ -14533,7 +14539,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
         <v>32</v>
       </c>
@@ -14562,7 +14568,7 @@
         <v>194.55</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
         <v>32</v>
       </c>
@@ -14591,7 +14597,7 @@
         <v>3088.05</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
         <v>32</v>
       </c>
@@ -14620,7 +14626,7 @@
         <v>1108.28</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
         <v>32</v>
       </c>
@@ -14649,7 +14655,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
         <v>32</v>
       </c>
@@ -14678,7 +14684,7 @@
         <v>-1524.66</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>32</v>
       </c>
@@ -14707,7 +14713,7 @@
         <v>3027.78</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
         <v>32</v>
       </c>
@@ -14736,7 +14742,7 @@
         <v>16101.58</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>32</v>
       </c>
@@ -14765,7 +14771,7 @@
         <v>2186.96</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>32</v>
       </c>
@@ -14794,7 +14800,7 @@
         <v>9694.93</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
         <v>32</v>
       </c>
@@ -14823,7 +14829,7 @@
         <v>32534.48</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
         <v>32</v>
       </c>
@@ -14852,7 +14858,7 @@
         <v>10830.54</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
         <v>32</v>
       </c>
@@ -14881,7 +14887,7 @@
         <v>14199.45</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
         <v>32</v>
       </c>
@@ -14910,7 +14916,7 @@
         <v>13427.35</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
         <v>32</v>
       </c>
@@ -14939,7 +14945,7 @@
         <v>8142.12</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
         <v>32</v>
       </c>
@@ -14968,7 +14974,7 @@
         <v>3529.11</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
         <v>32</v>
       </c>
@@ -14997,7 +15003,7 @@
         <v>20147.29</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
         <v>32</v>
       </c>
@@ -15026,7 +15032,7 @@
         <v>10944.45</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
         <v>32</v>
       </c>
@@ -15055,7 +15061,7 @@
         <v>175.57</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
         <v>32</v>
       </c>
@@ -15084,7 +15090,7 @@
         <v>2207.9699999999998</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
         <v>32</v>
       </c>
@@ -15113,7 +15119,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
         <v>32</v>
       </c>
@@ -15142,7 +15148,7 @@
         <v>1440.7</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
         <v>32</v>
       </c>
@@ -15171,7 +15177,7 @@
         <v>1418.6</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
         <v>32</v>
       </c>
@@ -15200,7 +15206,7 @@
         <v>345.49</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
         <v>32</v>
       </c>
@@ -15229,7 +15235,7 @@
         <v>603.15</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
         <v>32</v>
       </c>
@@ -15258,7 +15264,7 @@
         <v>64358.27</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
         <v>32</v>
       </c>
@@ -15287,7 +15293,7 @@
         <v>12957.6</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
         <v>32</v>
       </c>
@@ -15316,7 +15322,7 @@
         <v>2005.89</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
         <v>32</v>
       </c>
@@ -15345,7 +15351,7 @@
         <v>17964.52</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
         <v>32</v>
       </c>
@@ -15374,7 +15380,7 @@
         <v>1938.57</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
         <v>32</v>
       </c>
@@ -15403,7 +15409,7 @@
         <v>4300.74</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
         <v>32</v>
       </c>
@@ -15432,7 +15438,7 @@
         <v>135611.39000000001</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
         <v>32</v>
       </c>
@@ -15461,7 +15467,7 @@
         <v>11910.37</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
         <v>32</v>
       </c>
@@ -15490,7 +15496,7 @@
         <v>18240.47</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
         <v>32</v>
       </c>
@@ -15519,7 +15525,7 @@
         <v>6018.85</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
         <v>32</v>
       </c>
@@ -15548,7 +15554,7 @@
         <v>4945.09</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
         <v>32</v>
       </c>
@@ -15577,7 +15583,7 @@
         <v>4154.7</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
         <v>32</v>
       </c>
@@ -15606,7 +15612,7 @@
         <v>24783.279999999999</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
         <v>32</v>
       </c>
@@ -15635,7 +15641,7 @@
         <v>9239.77</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
         <v>32</v>
       </c>
@@ -15664,7 +15670,7 @@
         <v>37342.31</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
         <v>32</v>
       </c>
@@ -15693,7 +15699,7 @@
         <v>2590.37</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
         <v>32</v>
       </c>
@@ -15722,7 +15728,7 @@
         <v>438.46</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
         <v>32</v>
       </c>
@@ -15751,7 +15757,7 @@
         <v>461.29</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
         <v>32</v>
       </c>
@@ -15780,7 +15786,7 @@
         <v>699.36</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
         <v>32</v>
       </c>
@@ -15809,7 +15815,7 @@
         <v>49968.91</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
         <v>32</v>
       </c>
@@ -15838,7 +15844,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
         <v>32</v>
       </c>
@@ -15867,7 +15873,7 @@
         <v>33.14</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
         <v>32</v>
       </c>
@@ -15896,7 +15902,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
         <v>32</v>
       </c>
@@ -15925,7 +15931,7 @@
         <v>74.48</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
         <v>32</v>
       </c>
@@ -15954,7 +15960,7 @@
         <v>195.87</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
         <v>32</v>
       </c>
@@ -15983,7 +15989,7 @@
         <v>57.8</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
         <v>32</v>
       </c>
@@ -16012,7 +16018,7 @@
         <v>15.38</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A533" t="s">
         <v>32</v>
       </c>
@@ -16041,7 +16047,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
         <v>32</v>
       </c>
@@ -16070,7 +16076,7 @@
         <v>44.93</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
         <v>32</v>
       </c>
@@ -16099,7 +16105,7 @@
         <v>53.16</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
         <v>32</v>
       </c>
@@ -16128,7 +16134,7 @@
         <v>219.62</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
         <v>32</v>
       </c>
@@ -16157,7 +16163,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
         <v>32</v>
       </c>
@@ -16186,7 +16192,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
         <v>32</v>
       </c>
@@ -16215,7 +16221,7 @@
         <v>66.260000000000005</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
         <v>32</v>
       </c>
@@ -16244,7 +16250,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
         <v>32</v>
       </c>
@@ -16273,7 +16279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
         <v>32</v>
       </c>
@@ -16302,7 +16308,7 @@
         <v>222.22</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
         <v>32</v>
       </c>
@@ -16331,7 +16337,7 @@
         <v>15.34</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A544" t="s">
         <v>32</v>
       </c>
@@ -16360,7 +16366,7 @@
         <v>2746.34</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
         <v>32</v>
       </c>
@@ -16389,7 +16395,7 @@
         <v>1346.8</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A546" t="s">
         <v>32</v>
       </c>
@@ -16418,7 +16424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
         <v>32</v>
       </c>
@@ -16447,7 +16453,7 @@
         <v>666.1</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A548" t="s">
         <v>32</v>
       </c>
@@ -16476,7 +16482,7 @@
         <v>478.33</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A549" t="s">
         <v>32</v>
       </c>
@@ -16505,7 +16511,7 @@
         <v>512.55999999999995</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
         <v>32</v>
       </c>
@@ -16534,7 +16540,7 @@
         <v>513.1</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A551" t="s">
         <v>32</v>
       </c>
@@ -16563,7 +16569,7 @@
         <v>93.11</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A552" t="s">
         <v>32</v>
       </c>
@@ -16592,7 +16598,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
         <v>32</v>
       </c>
@@ -16621,7 +16627,7 @@
         <v>430.7</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A554" t="s">
         <v>32</v>
       </c>
@@ -16650,7 +16656,7 @@
         <v>201.5</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A555" t="s">
         <v>32</v>
       </c>
@@ -16679,7 +16685,7 @@
         <v>32.72</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A556" t="s">
         <v>32</v>
       </c>
@@ -16708,7 +16714,7 @@
         <v>122.37</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A557" t="s">
         <v>32</v>
       </c>
@@ -16737,7 +16743,7 @@
         <v>347.18</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A558" t="s">
         <v>32</v>
       </c>
@@ -16766,7 +16772,7 @@
         <v>348.73</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
         <v>32</v>
       </c>
@@ -16795,7 +16801,7 @@
         <v>211.11</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A560" t="s">
         <v>32</v>
       </c>
@@ -16824,7 +16830,7 @@
         <v>879.29</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A561" t="s">
         <v>32</v>
       </c>
@@ -16853,7 +16859,7 @@
         <v>414.31</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A562" t="s">
         <v>32</v>
       </c>
@@ -16882,7 +16888,7 @@
         <v>184.79</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A563" t="s">
         <v>32</v>
       </c>
@@ -16911,7 +16917,7 @@
         <v>554.99</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A564" t="s">
         <v>32</v>
       </c>
@@ -16940,7 +16946,7 @@
         <v>19895.77</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A565" t="s">
         <v>32</v>
       </c>
@@ -16969,7 +16975,7 @@
         <v>12150.71</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A566" t="s">
         <v>32</v>
       </c>
@@ -16998,7 +17004,7 @@
         <v>18274.419999999998</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A567" t="s">
         <v>32</v>
       </c>
@@ -17027,7 +17033,7 @@
         <v>15031.96</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
         <v>32</v>
       </c>
@@ -17056,7 +17062,7 @@
         <v>25951.19</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
         <v>32</v>
       </c>
@@ -17085,7 +17091,7 @@
         <v>15091</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A570" t="s">
         <v>32</v>
       </c>
@@ -17114,7 +17120,7 @@
         <v>12760.18</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A571" t="s">
         <v>32</v>
       </c>
@@ -17143,7 +17149,7 @@
         <v>85268.69</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A572" t="s">
         <v>32</v>
       </c>
@@ -17172,7 +17178,7 @@
         <v>90894.3</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A573" t="s">
         <v>32</v>
       </c>
@@ -17201,7 +17207,7 @@
         <v>125852.18</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A574" t="s">
         <v>32</v>
       </c>
@@ -17230,7 +17236,7 @@
         <v>99781.41</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A575" t="s">
         <v>32</v>
       </c>
@@ -17259,7 +17265,7 @@
         <v>107940.46</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A576" t="s">
         <v>32</v>
       </c>
@@ -17288,7 +17294,7 @@
         <v>129079.64</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
         <v>32</v>
       </c>
@@ -17317,7 +17323,7 @@
         <v>99687.61</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A578" t="s">
         <v>32</v>
       </c>
@@ -17346,7 +17352,7 @@
         <v>4177.22</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A579" t="s">
         <v>32</v>
       </c>
@@ -17375,7 +17381,7 @@
         <v>3609.41</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A580" t="s">
         <v>32</v>
       </c>
@@ -17404,7 +17410,7 @@
         <v>4458.66</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A581" t="s">
         <v>32</v>
       </c>
@@ -17433,7 +17439,7 @@
         <v>7922.4</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A582" t="s">
         <v>32</v>
       </c>
@@ -17462,7 +17468,7 @@
         <v>7979.57</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A583" t="s">
         <v>32</v>
       </c>
@@ -17491,7 +17497,7 @@
         <v>8458.7000000000007</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A584" t="s">
         <v>32</v>
       </c>
@@ -17520,7 +17526,7 @@
         <v>137.94</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A585" t="s">
         <v>32</v>
       </c>
@@ -17549,7 +17555,7 @@
         <v>4320</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
         <v>32</v>
       </c>
@@ -17578,7 +17584,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A587" t="s">
         <v>32</v>
       </c>
@@ -17607,7 +17613,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A588" t="s">
         <v>32</v>
       </c>
@@ -17636,7 +17642,7 @@
         <v>2115.16</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A589" t="s">
         <v>32</v>
       </c>
@@ -17665,7 +17671,7 @@
         <v>1129.1199999999999</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A590" t="s">
         <v>32</v>
       </c>
@@ -17694,7 +17700,7 @@
         <v>2123.3200000000002</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A591" t="s">
         <v>32</v>
       </c>
@@ -17723,7 +17729,7 @@
         <v>16072.28</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A592" t="s">
         <v>32</v>
       </c>
@@ -17752,7 +17758,7 @@
         <v>4350.3500000000004</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A593" t="s">
         <v>32</v>
       </c>
@@ -17781,7 +17787,7 @@
         <v>3558.65</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A594" t="s">
         <v>32</v>
       </c>
@@ -17810,7 +17816,7 @@
         <v>4739.33</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
         <v>32</v>
       </c>
@@ -17839,7 +17845,7 @@
         <v>226.31</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A596" t="s">
         <v>32</v>
       </c>
@@ -17868,7 +17874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A597" t="s">
         <v>32</v>
       </c>
@@ -17897,7 +17903,7 @@
         <v>-83.85</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A598" t="s">
         <v>32</v>
       </c>
@@ -17926,7 +17932,7 @@
         <v>1419.47</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A599" t="s">
         <v>32</v>
       </c>
@@ -17955,7 +17961,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A600" t="s">
         <v>32</v>
       </c>
@@ -17984,7 +17990,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A601" t="s">
         <v>32</v>
       </c>
@@ -18013,7 +18019,7 @@
         <v>41452.75</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A602" t="s">
         <v>32</v>
       </c>
@@ -18042,7 +18048,7 @@
         <v>24319.65</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A603" t="s">
         <v>32</v>
       </c>
@@ -18071,7 +18077,7 @@
         <v>34867.660000000003</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
         <v>32</v>
       </c>
@@ -18100,7 +18106,7 @@
         <v>40267.089999999997</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A605" t="s">
         <v>32</v>
       </c>
@@ -18129,7 +18135,7 @@
         <v>26114.06</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A606" t="s">
         <v>32</v>
       </c>
@@ -18158,7 +18164,7 @@
         <v>15.78</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A607" t="s">
         <v>32</v>
       </c>
@@ -18187,7 +18193,7 @@
         <v>183.18</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A608" t="s">
         <v>32</v>
       </c>
@@ -18216,7 +18222,7 @@
         <v>-559.29999999999995</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A609" t="s">
         <v>32</v>
       </c>
@@ -18245,7 +18251,7 @@
         <v>-4799.49</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A610" t="s">
         <v>32</v>
       </c>
@@ -18274,7 +18280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A611" t="s">
         <v>32</v>
       </c>
@@ -18303,7 +18309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A612" t="s">
         <v>32</v>
       </c>
@@ -18332,7 +18338,7 @@
         <v>105.8</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
         <v>32</v>
       </c>
@@ -18361,7 +18367,7 @@
         <v>37.32</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A614" t="s">
         <v>32</v>
       </c>
@@ -18390,7 +18396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A615" t="s">
         <v>32</v>
       </c>
@@ -18419,7 +18425,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A616" t="s">
         <v>32</v>
       </c>
@@ -18448,7 +18454,7 @@
         <v>33.9</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A617" t="s">
         <v>32</v>
       </c>
@@ -18477,7 +18483,7 @@
         <v>150.4</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A618" t="s">
         <v>32</v>
       </c>
@@ -18506,7 +18512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A619" t="s">
         <v>32</v>
       </c>
@@ -18535,7 +18541,7 @@
         <v>174.2</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A620" t="s">
         <v>32</v>
       </c>
@@ -18564,7 +18570,7 @@
         <v>188.15</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A621" t="s">
         <v>32</v>
       </c>
@@ -18593,7 +18599,7 @@
         <v>52.7</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
         <v>32</v>
       </c>
@@ -18622,7 +18628,7 @@
         <v>381.3</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A623" t="s">
         <v>32</v>
       </c>
@@ -18651,7 +18657,7 @@
         <v>210.36</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A624" t="s">
         <v>32</v>
       </c>
@@ -18680,7 +18686,7 @@
         <v>36.21</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A625" t="s">
         <v>32</v>
       </c>
@@ -18709,7 +18715,7 @@
         <v>22.37</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A626" t="s">
         <v>32</v>
       </c>
@@ -18738,7 +18744,7 @@
         <v>-485.26</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A627" t="s">
         <v>32</v>
       </c>
@@ -18767,7 +18773,7 @@
         <v>17.04</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A628" t="s">
         <v>32</v>
       </c>
@@ -18796,7 +18802,7 @@
         <v>23.74</v>
       </c>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A629" t="s">
         <v>32</v>
       </c>
@@ -18825,7 +18831,7 @@
         <v>1004.91</v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A630" t="s">
         <v>32</v>
       </c>
@@ -18854,7 +18860,7 @@
         <v>15518.32</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
         <v>32</v>
       </c>
@@ -18883,7 +18889,7 @@
         <v>17154.89</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A632" t="s">
         <v>32</v>
       </c>
@@ -18912,7 +18918,7 @@
         <v>21417.759999999998</v>
       </c>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A633" t="s">
         <v>32</v>
       </c>
@@ -18941,7 +18947,7 @@
         <v>15207.85</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A634" t="s">
         <v>32</v>
       </c>
@@ -18970,7 +18976,7 @@
         <v>15862.49</v>
       </c>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A635" t="s">
         <v>32</v>
       </c>
@@ -18999,7 +19005,7 @@
         <v>15872.13</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A636" t="s">
         <v>32</v>
       </c>
@@ -19028,7 +19034,7 @@
         <v>967.02</v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A637" t="s">
         <v>32</v>
       </c>
@@ -19057,7 +19063,7 @@
         <v>4479.5600000000004</v>
       </c>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A638" t="s">
         <v>32</v>
       </c>
@@ -19086,7 +19092,7 @@
         <v>200.5</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A639" t="s">
         <v>32</v>
       </c>
@@ -19115,7 +19121,7 @@
         <v>1627.12</v>
       </c>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
         <v>32</v>
       </c>
@@ -19144,7 +19150,7 @@
         <v>335.85</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A641" t="s">
         <v>32</v>
       </c>
@@ -19173,7 +19179,7 @@
         <v>179.42</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A642" t="s">
         <v>32</v>
       </c>
@@ -19202,7 +19208,7 @@
         <v>430.58</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A643" t="s">
         <v>32</v>
       </c>
@@ -19231,7 +19237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A644" t="s">
         <v>32</v>
       </c>
@@ -19260,7 +19266,7 @@
         <v>201.6</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A645" t="s">
         <v>32</v>
       </c>
@@ -19289,7 +19295,7 @@
         <v>169.48</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A646" t="s">
         <v>32</v>
       </c>
@@ -19318,7 +19324,7 @@
         <v>2710.71</v>
       </c>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A647" t="s">
         <v>32</v>
       </c>
@@ -19347,7 +19353,7 @@
         <v>2112.39</v>
       </c>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A648" t="s">
         <v>32</v>
       </c>
@@ -19376,7 +19382,7 @@
         <v>213.44</v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
         <v>32</v>
       </c>
@@ -19405,7 +19411,7 @@
         <v>1666.67</v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A650" t="s">
         <v>32</v>
       </c>
@@ -19434,7 +19440,7 @@
         <v>6924.58</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A651" t="s">
         <v>32</v>
       </c>
@@ -19463,7 +19469,7 @@
         <v>943.26</v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A652" t="s">
         <v>32</v>
       </c>
@@ -19492,7 +19498,7 @@
         <v>-1986.45</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A653" t="s">
         <v>32</v>
       </c>
@@ -19521,7 +19527,7 @@
         <v>1654.04</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A654" t="s">
         <v>32</v>
       </c>
@@ -19550,7 +19556,7 @@
         <v>446.7</v>
       </c>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A655" t="s">
         <v>32</v>
       </c>
@@ -19579,7 +19585,7 @@
         <v>13064.35</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A656" t="s">
         <v>32</v>
       </c>
@@ -19608,7 +19614,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A657" t="s">
         <v>32</v>
       </c>
@@ -19637,7 +19643,7 @@
         <v>1086.17</v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A658" t="s">
         <v>32</v>
       </c>
@@ -19666,7 +19672,7 @@
         <v>1259.29</v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A659" t="s">
         <v>32</v>
       </c>
@@ -19695,7 +19701,7 @@
         <v>1220.93</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A660" t="s">
         <v>32</v>
       </c>
@@ -19724,7 +19730,7 @@
         <v>1328.47</v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A661" t="s">
         <v>32</v>
       </c>
@@ -19753,7 +19759,7 @@
         <v>2988.25</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A662" t="s">
         <v>32</v>
       </c>
@@ -19782,7 +19788,7 @@
         <v>4858.09</v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A663" t="s">
         <v>32</v>
       </c>
@@ -19811,7 +19817,7 @@
         <v>916.65</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A664" t="s">
         <v>32</v>
       </c>
@@ -19840,7 +19846,7 @@
         <v>206.22</v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A665" t="s">
         <v>32</v>
       </c>
@@ -19869,7 +19875,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A666" t="s">
         <v>32</v>
       </c>
@@ -19898,7 +19904,7 @@
         <v>74.099999999999994</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A667" t="s">
         <v>32</v>
       </c>
@@ -19927,7 +19933,7 @@
         <v>115.1</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A668" t="s">
         <v>32</v>
       </c>
@@ -19956,7 +19962,7 @@
         <v>1655.42</v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A669" t="s">
         <v>32</v>
       </c>
@@ -19985,7 +19991,7 @@
         <v>2457.8200000000002</v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A670" t="s">
         <v>32</v>
       </c>
@@ -20014,7 +20020,7 @@
         <v>987.17</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A671" t="s">
         <v>32</v>
       </c>
@@ -20043,7 +20049,7 @@
         <v>2652.17</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A672" t="s">
         <v>32</v>
       </c>
@@ -20072,7 +20078,7 @@
         <v>2515.5700000000002</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A673" t="s">
         <v>32</v>
       </c>
@@ -20101,7 +20107,7 @@
         <v>862.51</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A674" t="s">
         <v>32</v>
       </c>
@@ -20130,7 +20136,7 @@
         <v>629.55999999999995</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A675" t="s">
         <v>32</v>
       </c>
@@ -20159,7 +20165,7 @@
         <v>486.07</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A676" t="s">
         <v>32</v>
       </c>
@@ -20188,7 +20194,7 @@
         <v>160.58000000000001</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A677" t="s">
         <v>32</v>
       </c>
@@ -20217,7 +20223,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A678" t="s">
         <v>32</v>
       </c>
@@ -20246,7 +20252,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A679" t="s">
         <v>32</v>
       </c>
@@ -20275,7 +20281,7 @@
         <v>2223.6</v>
       </c>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A680" t="s">
         <v>32</v>
       </c>
@@ -20304,7 +20310,7 @@
         <v>42.16</v>
       </c>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A681" t="s">
         <v>32</v>
       </c>
@@ -20333,7 +20339,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A682" t="s">
         <v>32</v>
       </c>
@@ -20362,7 +20368,7 @@
         <v>2786.29</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A683" t="s">
         <v>32</v>
       </c>
@@ -20391,7 +20397,7 @@
         <v>136.37</v>
       </c>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A684" t="s">
         <v>32</v>
       </c>
@@ -20420,7 +20426,7 @@
         <v>108.75</v>
       </c>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A685" t="s">
         <v>32</v>
       </c>
@@ -20449,7 +20455,7 @@
         <v>5587.5</v>
       </c>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A686" t="s">
         <v>32</v>
       </c>
@@ -20478,7 +20484,7 @@
         <v>-28</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A687" t="s">
         <v>32</v>
       </c>
@@ -20507,7 +20513,7 @@
         <v>12263.44</v>
       </c>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A688" t="s">
         <v>32</v>
       </c>
@@ -20536,7 +20542,7 @@
         <v>30363.58</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A689" t="s">
         <v>32</v>
       </c>
@@ -20565,7 +20571,7 @@
         <v>50358.42</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A690" t="s">
         <v>32</v>
       </c>
@@ -20594,7 +20600,7 @@
         <v>17946.060000000001</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A691" t="s">
         <v>32</v>
       </c>
@@ -20623,7 +20629,7 @@
         <v>10950.89</v>
       </c>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A692" t="s">
         <v>32</v>
       </c>
@@ -20652,7 +20658,7 @@
         <v>12211.91</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A693" t="s">
         <v>32</v>
       </c>
@@ -20681,7 +20687,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A694" t="s">
         <v>32</v>
       </c>
@@ -20710,7 +20716,7 @@
         <v>1693.83</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A695" t="s">
         <v>32</v>
       </c>
@@ -20739,7 +20745,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A696" t="s">
         <v>32</v>
       </c>
@@ -20768,7 +20774,7 @@
         <v>2660.72</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A697" t="s">
         <v>32</v>
       </c>
@@ -20797,7 +20803,7 @@
         <v>290.8</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A698" t="s">
         <v>32</v>
       </c>
@@ -20826,7 +20832,7 @@
         <v>263.42</v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A699" t="s">
         <v>32</v>
       </c>
@@ -20855,7 +20861,7 @@
         <v>83.57</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A700" t="s">
         <v>32</v>
       </c>
@@ -20884,7 +20890,7 @@
         <v>42.16</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A701" t="s">
         <v>32</v>
       </c>
@@ -20913,7 +20919,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A702" t="s">
         <v>32</v>
       </c>
@@ -20942,7 +20948,7 @@
         <v>445.3</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A703" t="s">
         <v>32</v>
       </c>
@@ -20971,7 +20977,7 @@
         <v>1382.02</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A704" t="s">
         <v>32</v>
       </c>
@@ -21000,7 +21006,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A705" t="s">
         <v>32</v>
       </c>
@@ -21029,7 +21035,7 @@
         <v>904.74</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A706" t="s">
         <v>32</v>
       </c>
@@ -21058,7 +21064,7 @@
         <v>495.62</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A707" t="s">
         <v>32</v>
       </c>
@@ -21087,7 +21093,7 @@
         <v>6834.46</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A708" t="s">
         <v>32</v>
       </c>
@@ -21116,7 +21122,7 @@
         <v>4356.47</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A709" t="s">
         <v>32</v>
       </c>
@@ -21145,7 +21151,7 @@
         <v>2296.96</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A710" t="s">
         <v>32</v>
       </c>
@@ -21174,7 +21180,7 @@
         <v>2369.4</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A711" t="s">
         <v>32</v>
       </c>
@@ -21203,7 +21209,7 @@
         <v>2032.79</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A712" t="s">
         <v>32</v>
       </c>
@@ -21232,7 +21238,7 @@
         <v>510.85</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A713" t="s">
         <v>32</v>
       </c>
@@ -21261,7 +21267,7 @@
         <v>295.11</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="714" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A714" t="s">
         <v>32</v>
       </c>
@@ -21290,7 +21296,7 @@
         <v>-479.97</v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A715" t="s">
         <v>32</v>
       </c>
@@ -21319,7 +21325,7 @@
         <v>178.45</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="716" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A716" t="s">
         <v>32</v>
       </c>
@@ -21348,7 +21354,7 @@
         <v>536.35</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A717" t="s">
         <v>32</v>
       </c>
@@ -21377,7 +21383,7 @@
         <v>97.12</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A718" t="s">
         <v>32</v>
       </c>
@@ -21406,7 +21412,7 @@
         <v>114.59</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A719" t="s">
         <v>32</v>
       </c>
@@ -21435,7 +21441,7 @@
         <v>171.9</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="720" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A720" t="s">
         <v>32</v>
       </c>
@@ -21464,7 +21470,7 @@
         <v>307.38</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="721" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A721" t="s">
         <v>32</v>
       </c>
@@ -21493,7 +21499,7 @@
         <v>372.6</v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="722" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A722" t="s">
         <v>32</v>
       </c>
@@ -21522,7 +21528,7 @@
         <v>121.09</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="723" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A723" t="s">
         <v>32</v>
       </c>
@@ -21551,7 +21557,7 @@
         <v>52.32</v>
       </c>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="724" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A724" t="s">
         <v>32</v>
       </c>
@@ -21580,7 +21586,7 @@
         <v>27.06</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="725" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A725" t="s">
         <v>32</v>
       </c>
@@ -21609,7 +21615,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="726" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A726" t="s">
         <v>32</v>
       </c>
@@ -21638,7 +21644,7 @@
         <v>113.3</v>
       </c>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="727" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A727" t="s">
         <v>32</v>
       </c>
@@ -21667,7 +21673,7 @@
         <v>1241.8900000000001</v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="728" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A728" t="s">
         <v>32</v>
       </c>
@@ -21696,7 +21702,7 @@
         <v>147.32</v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="729" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A729" t="s">
         <v>32</v>
       </c>
@@ -21725,7 +21731,7 @@
         <v>463.99</v>
       </c>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="730" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A730" t="s">
         <v>32</v>
       </c>
@@ -21754,7 +21760,7 @@
         <v>4280.07</v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="731" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A731" t="s">
         <v>32</v>
       </c>
@@ -21783,7 +21789,7 @@
         <v>2117.81</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="732" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A732" t="s">
         <v>32</v>
       </c>
@@ -21812,7 +21818,7 @@
         <v>18015.02</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="733" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A733" t="s">
         <v>32</v>
       </c>
@@ -21841,7 +21847,7 @@
         <v>8384.85</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="734" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A734" t="s">
         <v>32</v>
       </c>
@@ -21870,7 +21876,7 @@
         <v>24645.95</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="735" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A735" t="s">
         <v>32</v>
       </c>
@@ -21899,7 +21905,7 @@
         <v>5448.03</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="736" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A736" t="s">
         <v>32</v>
       </c>
@@ -21928,7 +21934,7 @@
         <v>11672.59</v>
       </c>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="737" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A737" t="s">
         <v>32</v>
       </c>
@@ -21957,7 +21963,7 @@
         <v>18196.310000000001</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="738" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A738" t="s">
         <v>32</v>
       </c>
@@ -21986,7 +21992,7 @@
         <v>1508.1</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="739" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A739" t="s">
         <v>32</v>
       </c>
@@ -22015,7 +22021,7 @@
         <v>750.41</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="740" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A740" t="s">
         <v>32</v>
       </c>
@@ -22044,7 +22050,7 @@
         <v>136.97999999999999</v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="741" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A741" t="s">
         <v>32</v>
       </c>
@@ -22073,7 +22079,7 @@
         <v>158.41</v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="742" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A742" t="s">
         <v>32</v>
       </c>
@@ -22102,7 +22108,7 @@
         <v>921.9</v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="743" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A743" t="s">
         <v>32</v>
       </c>
@@ -22131,7 +22137,7 @@
         <v>248.86</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="744" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A744" t="s">
         <v>32</v>
       </c>
@@ -22160,7 +22166,7 @@
         <v>215.04</v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="745" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A745" t="s">
         <v>32</v>
       </c>
@@ -22189,7 +22195,7 @@
         <v>-1.7763568394002501E-15</v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="746" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A746" t="s">
         <v>32</v>
       </c>
@@ -22218,7 +22224,7 @@
         <v>669.96</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="747" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A747" t="s">
         <v>32</v>
       </c>
@@ -22247,7 +22253,7 @@
         <v>43751.69</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="748" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A748" t="s">
         <v>32</v>
       </c>
@@ -22276,7 +22282,7 @@
         <v>19147.55</v>
       </c>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="749" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A749" t="s">
         <v>32</v>
       </c>
@@ -22305,7 +22311,7 @@
         <v>36068.129999999997</v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="750" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A750" t="s">
         <v>32</v>
       </c>
@@ -22334,7 +22340,7 @@
         <v>37478.83</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="751" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A751" t="s">
         <v>32</v>
       </c>
@@ -22363,7 +22369,7 @@
         <v>40578.89</v>
       </c>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="752" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A752" t="s">
         <v>32</v>
       </c>
@@ -22392,7 +22398,7 @@
         <v>1416.12</v>
       </c>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="753" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A753" t="s">
         <v>32</v>
       </c>
@@ -22421,7 +22427,7 @@
         <v>218.9</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="754" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A754" t="s">
         <v>32</v>
       </c>
@@ -22450,7 +22456,7 @@
         <v>-750</v>
       </c>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="755" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A755" t="s">
         <v>32</v>
       </c>
@@ -22479,7 +22485,7 @@
         <v>-125.04</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="756" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A756" t="s">
         <v>32</v>
       </c>
@@ -22508,7 +22514,7 @@
         <v>35283.03</v>
       </c>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="757" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A757" t="s">
         <v>32</v>
       </c>
@@ -22537,7 +22543,7 @@
         <v>106659.59</v>
       </c>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="758" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A758" t="s">
         <v>32</v>
       </c>
@@ -22566,7 +22572,7 @@
         <v>22493.91</v>
       </c>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="759" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A759" t="s">
         <v>32</v>
       </c>
@@ -22595,7 +22601,7 @@
         <v>55568.07</v>
       </c>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="760" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A760" t="s">
         <v>32</v>
       </c>
@@ -22624,7 +22630,7 @@
         <v>52589.65</v>
       </c>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="761" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A761" t="s">
         <v>32</v>
       </c>
@@ -22653,7 +22659,7 @@
         <v>18102.59</v>
       </c>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="762" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A762" t="s">
         <v>32</v>
       </c>
@@ -22682,7 +22688,7 @@
         <v>665.77</v>
       </c>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="763" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A763" t="s">
         <v>32</v>
       </c>
@@ -22711,7 +22717,7 @@
         <v>266.81</v>
       </c>
     </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="764" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A764" t="s">
         <v>32</v>
       </c>
@@ -22740,7 +22746,7 @@
         <v>81.39</v>
       </c>
     </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="765" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A765" t="s">
         <v>32</v>
       </c>
@@ -22769,7 +22775,7 @@
         <v>285.18</v>
       </c>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="766" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A766" t="s">
         <v>32</v>
       </c>
@@ -22798,7 +22804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="767" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="767" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A767" t="s">
         <v>32</v>
       </c>
@@ -22827,7 +22833,7 @@
         <v>1754.97</v>
       </c>
     </row>
-    <row r="768" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="768" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A768" t="s">
         <v>32</v>
       </c>
@@ -22856,7 +22862,7 @@
         <v>299.06</v>
       </c>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="769" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A769" t="s">
         <v>32</v>
       </c>
@@ -22885,7 +22891,7 @@
         <v>464.03</v>
       </c>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="770" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A770" t="s">
         <v>32</v>
       </c>
@@ -22914,7 +22920,7 @@
         <v>432.63</v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="771" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A771" t="s">
         <v>32</v>
       </c>
@@ -22943,7 +22949,7 @@
         <v>632.14</v>
       </c>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="772" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A772" t="s">
         <v>32</v>
       </c>
@@ -22972,7 +22978,7 @@
         <v>1850.45</v>
       </c>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="773" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A773" t="s">
         <v>32</v>
       </c>
@@ -23001,7 +23007,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="774" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A774" t="s">
         <v>32</v>
       </c>
@@ -23030,7 +23036,7 @@
         <v>642.57000000000005</v>
       </c>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="775" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A775" t="s">
         <v>32</v>
       </c>
@@ -23059,7 +23065,7 @@
         <v>4566</v>
       </c>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="776" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A776" t="s">
         <v>32</v>
       </c>
@@ -23088,7 +23094,7 @@
         <v>-626.84</v>
       </c>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="777" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A777" t="s">
         <v>32</v>
       </c>
@@ -23117,7 +23123,7 @@
         <v>-646.71</v>
       </c>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="778" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A778" t="s">
         <v>32</v>
       </c>
@@ -23146,7 +23152,7 @@
         <v>11197.52</v>
       </c>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="779" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A779" t="s">
         <v>32</v>
       </c>
@@ -23175,7 +23181,7 @@
         <v>6773.82</v>
       </c>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="780" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A780" t="s">
         <v>32</v>
       </c>
@@ -23204,7 +23210,7 @@
         <v>6873.52</v>
       </c>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="781" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A781" t="s">
         <v>32</v>
       </c>
@@ -23233,7 +23239,7 @@
         <v>11745.66</v>
       </c>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="782" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A782" t="s">
         <v>32</v>
       </c>
@@ -23262,7 +23268,7 @@
         <v>13237.8</v>
       </c>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="783" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A783" t="s">
         <v>32</v>
       </c>
@@ -23291,7 +23297,7 @@
         <v>26541.34</v>
       </c>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="784" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A784" t="s">
         <v>32</v>
       </c>
@@ -23320,7 +23326,7 @@
         <v>6865.56</v>
       </c>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="785" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A785" t="s">
         <v>32</v>
       </c>
@@ -23349,7 +23355,7 @@
         <v>47.72</v>
       </c>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="786" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A786" t="s">
         <v>32</v>
       </c>
@@ -23378,7 +23384,7 @@
         <v>187.73</v>
       </c>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="787" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A787" t="s">
         <v>32</v>
       </c>
@@ -23407,7 +23413,7 @@
         <v>35.07</v>
       </c>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="788" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A788" t="s">
         <v>32</v>
       </c>
@@ -23436,7 +23442,7 @@
         <v>254.64</v>
       </c>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="789" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A789" t="s">
         <v>32</v>
       </c>
@@ -23465,7 +23471,7 @@
         <v>1702.05</v>
       </c>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="790" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A790" t="s">
         <v>32</v>
       </c>
@@ -23494,7 +23500,7 @@
         <v>1058.6400000000001</v>
       </c>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="791" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A791" t="s">
         <v>32</v>
       </c>
@@ -23523,7 +23529,7 @@
         <v>28.27</v>
       </c>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="792" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A792" t="s">
         <v>32</v>
       </c>
@@ -23552,7 +23558,7 @@
         <v>458.33</v>
       </c>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="793" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A793" t="s">
         <v>32</v>
       </c>
@@ -23581,7 +23587,7 @@
         <v>61.07</v>
       </c>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="794" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A794" t="s">
         <v>32</v>
       </c>
@@ -23610,7 +23616,7 @@
         <v>1200.98</v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="795" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A795" t="s">
         <v>32</v>
       </c>
@@ -23639,7 +23645,7 @@
         <v>155.62</v>
       </c>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="796" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A796" t="s">
         <v>32</v>
       </c>
@@ -23668,7 +23674,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="797" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A797" t="s">
         <v>32</v>
       </c>
@@ -23697,7 +23703,7 @@
         <v>716.47</v>
       </c>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="798" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A798" t="s">
         <v>32</v>
       </c>
@@ -23726,7 +23732,7 @@
         <v>196.37</v>
       </c>
     </row>
-    <row r="799" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="799" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A799" t="s">
         <v>32</v>
       </c>
@@ -23755,7 +23761,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="800" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="800" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A800" t="s">
         <v>32</v>
       </c>
@@ -23784,7 +23790,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="801" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="801" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A801" t="s">
         <v>32</v>
       </c>
@@ -23813,7 +23819,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="802" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="802" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A802" t="s">
         <v>32</v>
       </c>
@@ -23842,7 +23848,7 @@
         <v>34.22</v>
       </c>
     </row>
-    <row r="803" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="803" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A803" t="s">
         <v>32</v>
       </c>
@@ -23871,7 +23877,7 @@
         <v>392.56</v>
       </c>
     </row>
-    <row r="804" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="804" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A804" t="s">
         <v>32</v>
       </c>
@@ -23900,7 +23906,7 @@
         <v>17375.8</v>
       </c>
     </row>
-    <row r="805" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="805" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A805" t="s">
         <v>32</v>
       </c>
@@ -23929,7 +23935,7 @@
         <v>21786.03</v>
       </c>
     </row>
-    <row r="806" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="806" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A806" t="s">
         <v>32</v>
       </c>
@@ -23958,7 +23964,7 @@
         <v>24373.81</v>
       </c>
     </row>
-    <row r="807" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="807" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A807" t="s">
         <v>32</v>
       </c>
@@ -23987,7 +23993,7 @@
         <v>367.58</v>
       </c>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="808" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A808" t="s">
         <v>32</v>
       </c>
@@ -24016,7 +24022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="809" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="809" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A809" t="s">
         <v>32</v>
       </c>
@@ -24045,7 +24051,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="810" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A810" t="s">
         <v>32</v>
       </c>
@@ -24074,7 +24080,7 @@
         <v>90.19</v>
       </c>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="811" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A811" t="s">
         <v>32</v>
       </c>
@@ -24103,7 +24109,7 @@
         <v>29.78</v>
       </c>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="812" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A812" t="s">
         <v>32</v>
       </c>
@@ -24132,7 +24138,7 @@
         <v>15.09</v>
       </c>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="813" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A813" t="s">
         <v>32</v>
       </c>
@@ -24161,7 +24167,7 @@
         <v>131.4</v>
       </c>
     </row>
-    <row r="814" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="814" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A814" t="s">
         <v>32</v>
       </c>
@@ -24190,7 +24196,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="815" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="815" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A815" t="s">
         <v>32</v>
       </c>
@@ -24219,7 +24225,7 @@
         <v>144.66</v>
       </c>
     </row>
-    <row r="816" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="816" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A816" t="s">
         <v>32</v>
       </c>
@@ -24248,7 +24254,7 @@
         <v>728.52</v>
       </c>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="817" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A817" t="s">
         <v>32</v>
       </c>
@@ -24277,7 +24283,7 @@
         <v>678.14</v>
       </c>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="818" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A818" t="s">
         <v>32</v>
       </c>
@@ -24306,7 +24312,7 @@
         <v>7766</v>
       </c>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="819" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A819" t="s">
         <v>32</v>
       </c>
@@ -24335,7 +24341,7 @@
         <v>4683.3</v>
       </c>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="820" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A820" t="s">
         <v>32</v>
       </c>
@@ -24364,7 +24370,7 @@
         <v>31464.27</v>
       </c>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="821" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A821" t="s">
         <v>32</v>
       </c>
@@ -24393,7 +24399,7 @@
         <v>28037.17</v>
       </c>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="822" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A822" t="s">
         <v>32</v>
       </c>
@@ -24422,7 +24428,7 @@
         <v>15425.04</v>
       </c>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="823" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A823" t="s">
         <v>32</v>
       </c>
@@ -24451,7 +24457,7 @@
         <v>55308.05</v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="824" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A824" t="s">
         <v>32</v>
       </c>
@@ -24480,7 +24486,7 @@
         <v>104502.8</v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="825" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A825" t="s">
         <v>32</v>
       </c>
@@ -24509,7 +24515,7 @@
         <v>82250.63</v>
       </c>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="826" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A826" t="s">
         <v>32</v>
       </c>
@@ -24538,7 +24544,7 @@
         <v>51157.87</v>
       </c>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="827" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A827" t="s">
         <v>32</v>
       </c>
@@ -24567,7 +24573,7 @@
         <v>55710.48</v>
       </c>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="828" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A828" t="s">
         <v>32</v>
       </c>
@@ -24596,7 +24602,7 @@
         <v>-237.98</v>
       </c>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="829" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A829" t="s">
         <v>32</v>
       </c>
@@ -24625,7 +24631,7 @@
         <v>1286.47</v>
       </c>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="830" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A830" t="s">
         <v>32</v>
       </c>
@@ -24654,7 +24660,7 @@
         <v>-1459.11</v>
       </c>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="831" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A831" t="s">
         <v>32</v>
       </c>
@@ -24683,7 +24689,7 @@
         <v>-1073.08</v>
       </c>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="832" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A832" t="s">
         <v>32</v>
       </c>
@@ -24712,7 +24718,7 @@
         <v>-1973.82</v>
       </c>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="833" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A833" t="s">
         <v>32</v>
       </c>
@@ -24741,7 +24747,7 @@
         <v>14898.21</v>
       </c>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="834" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A834" t="s">
         <v>32</v>
       </c>
@@ -24770,7 +24776,7 @@
         <v>-2958.9</v>
       </c>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="835" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A835" t="s">
         <v>32</v>
       </c>
@@ -24799,7 +24805,7 @@
         <v>269267.62</v>
       </c>
     </row>
-    <row r="836" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="836" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A836" t="s">
         <v>32</v>
       </c>
@@ -24828,7 +24834,7 @@
         <v>332867.09999999998</v>
       </c>
     </row>
-    <row r="837" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="837" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A837" t="s">
         <v>32</v>
       </c>
@@ -24857,7 +24863,7 @@
         <v>277673.84000000003</v>
       </c>
     </row>
-    <row r="838" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="838" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A838" t="s">
         <v>32</v>
       </c>
@@ -24886,7 +24892,7 @@
         <v>317064.48</v>
       </c>
     </row>
-    <row r="839" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="839" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A839" t="s">
         <v>32</v>
       </c>
@@ -24915,7 +24921,7 @@
         <v>271966.87</v>
       </c>
     </row>
-    <row r="840" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="840" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A840" t="s">
         <v>32</v>
       </c>
@@ -24944,7 +24950,7 @@
         <v>499512.99</v>
       </c>
     </row>
-    <row r="841" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="841" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A841" t="s">
         <v>32</v>
       </c>
@@ -24973,7 +24979,7 @@
         <v>359473.35</v>
       </c>
     </row>
-    <row r="842" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="842" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A842" t="s">
         <v>32</v>
       </c>
@@ -25002,7 +25008,7 @@
         <v>338.94</v>
       </c>
     </row>
-    <row r="843" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="843" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A843" t="s">
         <v>32</v>
       </c>
@@ -25031,7 +25037,7 @@
         <v>10.33</v>
       </c>
     </row>
-    <row r="844" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="844" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A844" t="s">
         <v>32</v>
       </c>
@@ -25060,7 +25066,7 @@
         <v>24.54</v>
       </c>
     </row>
-    <row r="845" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="845" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A845" t="s">
         <v>32</v>
       </c>
@@ -25089,7 +25095,7 @@
         <v>55.49</v>
       </c>
     </row>
-    <row r="846" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="846" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A846" t="s">
         <v>32</v>
       </c>
@@ -25118,7 +25124,7 @@
         <v>1574.76</v>
       </c>
     </row>
-    <row r="847" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="847" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A847" t="s">
         <v>32</v>
       </c>
@@ -25147,7 +25153,7 @@
         <v>278.14999999999998</v>
       </c>
     </row>
-    <row r="848" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="848" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A848" t="s">
         <v>32</v>
       </c>
@@ -25176,7 +25182,7 @@
         <v>40.049999999999997</v>
       </c>
     </row>
-    <row r="849" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="849" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A849" t="s">
         <v>32</v>
       </c>
@@ -25205,7 +25211,7 @@
         <v>2290.88</v>
       </c>
     </row>
-    <row r="850" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="850" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A850" t="s">
         <v>32</v>
       </c>
@@ -25234,7 +25240,7 @@
         <v>107.47</v>
       </c>
     </row>
-    <row r="851" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="851" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A851" t="s">
         <v>32</v>
       </c>
@@ -25263,7 +25269,7 @@
         <v>125.4</v>
       </c>
     </row>
-    <row r="852" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="852" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A852" t="s">
         <v>32</v>
       </c>
@@ -25292,7 +25298,7 @@
         <v>945.85</v>
       </c>
     </row>
-    <row r="853" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="853" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A853" t="s">
         <v>32</v>
       </c>
@@ -25321,7 +25327,7 @@
         <v>12.08</v>
       </c>
     </row>
-    <row r="854" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="854" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A854" t="s">
         <v>32</v>
       </c>
@@ -25350,7 +25356,7 @@
         <v>197.01</v>
       </c>
     </row>
-    <row r="855" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="855" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A855" t="s">
         <v>32</v>
       </c>
@@ -25379,7 +25385,7 @@
         <v>5029.83</v>
       </c>
     </row>
-    <row r="856" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="856" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A856" t="s">
         <v>32</v>
       </c>
@@ -25408,7 +25414,7 @@
         <v>4104.68</v>
       </c>
     </row>
-    <row r="857" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="857" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A857" t="s">
         <v>32</v>
       </c>
@@ -25437,7 +25443,7 @@
         <v>8916.1</v>
       </c>
     </row>
-    <row r="858" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="858" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A858" t="s">
         <v>32</v>
       </c>
@@ -25466,7 +25472,7 @@
         <v>7108.07</v>
       </c>
     </row>
-    <row r="859" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="859" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A859" t="s">
         <v>32</v>
       </c>
@@ -25495,7 +25501,7 @@
         <v>22032.95</v>
       </c>
     </row>
-    <row r="860" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="860" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A860" t="s">
         <v>32</v>
       </c>
@@ -25524,7 +25530,7 @@
         <v>13274.16</v>
       </c>
     </row>
-    <row r="861" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="861" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A861" t="s">
         <v>32</v>
       </c>
@@ -25553,7 +25559,7 @@
         <v>1446.79</v>
       </c>
     </row>
-    <row r="862" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="862" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A862" t="s">
         <v>32</v>
       </c>
@@ -25582,7 +25588,7 @@
         <v>308.55</v>
       </c>
     </row>
-    <row r="863" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="863" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A863" t="s">
         <v>32</v>
       </c>
@@ -25611,7 +25617,7 @@
         <v>483.47</v>
       </c>
     </row>
-    <row r="864" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="864" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A864" t="s">
         <v>32</v>
       </c>
@@ -25640,7 +25646,7 @@
         <v>377.53</v>
       </c>
     </row>
-    <row r="865" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="865" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A865" t="s">
         <v>32</v>
       </c>
@@ -25669,7 +25675,7 @@
         <v>777.69</v>
       </c>
     </row>
-    <row r="866" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="866" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A866" t="s">
         <v>32</v>
       </c>
@@ -25698,7 +25704,7 @@
         <v>721.17</v>
       </c>
     </row>
-    <row r="867" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="867" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A867" t="s">
         <v>32</v>
       </c>
@@ -25727,7 +25733,7 @@
         <v>1641.44</v>
       </c>
     </row>
-    <row r="868" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="868" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A868" t="s">
         <v>32</v>
       </c>
@@ -25756,7 +25762,7 @@
         <v>106.43</v>
       </c>
     </row>
-    <row r="869" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="869" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A869" t="s">
         <v>32</v>
       </c>
@@ -25785,7 +25791,7 @@
         <v>34.67</v>
       </c>
     </row>
-    <row r="870" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="870" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A870" t="s">
         <v>32</v>
       </c>
@@ -25814,7 +25820,7 @@
         <v>26.88</v>
       </c>
     </row>
-    <row r="871" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="871" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A871" t="s">
         <v>32</v>
       </c>
@@ -25843,7 +25849,7 @@
         <v>12.43</v>
       </c>
     </row>
-    <row r="872" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="872" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A872" t="s">
         <v>32</v>
       </c>
@@ -25872,7 +25878,7 @@
         <v>489.61</v>
       </c>
     </row>
-    <row r="873" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="873" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A873" t="s">
         <v>32</v>
       </c>
@@ -25901,7 +25907,7 @@
         <v>931.8</v>
       </c>
     </row>
-    <row r="874" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="874" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A874" t="s">
         <v>32</v>
       </c>
@@ -25930,7 +25936,7 @@
         <v>63.25</v>
       </c>
     </row>
-    <row r="875" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="875" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
       <c r="A875" t="s">
         <v>32</v>
       </c>
@@ -25959,8 +25965,721 @@
         <v>147.84</v>
       </c>
     </row>
+    <row r="876" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A876" t="s">
+        <v>32</v>
+      </c>
+      <c r="B876" t="s">
+        <v>1</v>
+      </c>
+      <c r="C876">
+        <v>10031</v>
+      </c>
+      <c r="D876" t="s">
+        <v>14</v>
+      </c>
+      <c r="E876" t="s">
+        <v>19</v>
+      </c>
+      <c r="F876" t="s">
+        <v>24</v>
+      </c>
+      <c r="G876" t="s">
+        <v>2</v>
+      </c>
+      <c r="H876" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I876">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="877" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A877" t="s">
+        <v>32</v>
+      </c>
+      <c r="B877" t="s">
+        <v>1</v>
+      </c>
+      <c r="C877">
+        <v>10031</v>
+      </c>
+      <c r="D877" t="s">
+        <v>14</v>
+      </c>
+      <c r="E877" t="s">
+        <v>19</v>
+      </c>
+      <c r="F877" t="s">
+        <v>24</v>
+      </c>
+      <c r="G877" t="s">
+        <v>3</v>
+      </c>
+      <c r="H877" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I877">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="878" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A878" t="s">
+        <v>32</v>
+      </c>
+      <c r="B878" t="s">
+        <v>1</v>
+      </c>
+      <c r="C878">
+        <v>10031</v>
+      </c>
+      <c r="D878" t="s">
+        <v>14</v>
+      </c>
+      <c r="E878" t="s">
+        <v>19</v>
+      </c>
+      <c r="F878" t="s">
+        <v>24</v>
+      </c>
+      <c r="G878" t="s">
+        <v>8</v>
+      </c>
+      <c r="H878" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I878">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="879" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A879" t="s">
+        <v>32</v>
+      </c>
+      <c r="B879" t="s">
+        <v>1</v>
+      </c>
+      <c r="C879">
+        <v>10031</v>
+      </c>
+      <c r="D879" t="s">
+        <v>14</v>
+      </c>
+      <c r="E879" t="s">
+        <v>19</v>
+      </c>
+      <c r="F879" t="s">
+        <v>24</v>
+      </c>
+      <c r="G879" t="s">
+        <v>9</v>
+      </c>
+      <c r="H879" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I879">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="880" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A880" t="s">
+        <v>32</v>
+      </c>
+      <c r="B880" t="s">
+        <v>1</v>
+      </c>
+      <c r="C880">
+        <v>10031</v>
+      </c>
+      <c r="D880" t="s">
+        <v>14</v>
+      </c>
+      <c r="E880" t="s">
+        <v>19</v>
+      </c>
+      <c r="F880" t="s">
+        <v>24</v>
+      </c>
+      <c r="G880" t="s">
+        <v>10</v>
+      </c>
+      <c r="H880" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I880">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="881" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A881" t="s">
+        <v>32</v>
+      </c>
+      <c r="B881" t="s">
+        <v>1</v>
+      </c>
+      <c r="C881">
+        <v>10031</v>
+      </c>
+      <c r="D881" t="s">
+        <v>14</v>
+      </c>
+      <c r="E881" t="s">
+        <v>19</v>
+      </c>
+      <c r="F881" t="s">
+        <v>24</v>
+      </c>
+      <c r="G881" t="s">
+        <v>11</v>
+      </c>
+      <c r="H881" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I881">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="882" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A882" t="s">
+        <v>32</v>
+      </c>
+      <c r="B882" t="s">
+        <v>1</v>
+      </c>
+      <c r="C882">
+        <v>10031</v>
+      </c>
+      <c r="D882" t="s">
+        <v>14</v>
+      </c>
+      <c r="E882" t="s">
+        <v>19</v>
+      </c>
+      <c r="F882" t="s">
+        <v>24</v>
+      </c>
+      <c r="G882" t="s">
+        <v>12</v>
+      </c>
+      <c r="H882" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I882">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="883" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A883" t="s">
+        <v>32</v>
+      </c>
+      <c r="B883" t="s">
+        <v>1</v>
+      </c>
+      <c r="C883">
+        <v>10031</v>
+      </c>
+      <c r="D883" t="s">
+        <v>14</v>
+      </c>
+      <c r="E883" t="s">
+        <v>19</v>
+      </c>
+      <c r="F883" t="s">
+        <v>25</v>
+      </c>
+      <c r="G883" t="s">
+        <v>13</v>
+      </c>
+      <c r="H883" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I883">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="884" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A884" t="s">
+        <v>32</v>
+      </c>
+      <c r="B884" t="s">
+        <v>1</v>
+      </c>
+      <c r="C884">
+        <v>10031</v>
+      </c>
+      <c r="D884" t="s">
+        <v>14</v>
+      </c>
+      <c r="E884" t="s">
+        <v>19</v>
+      </c>
+      <c r="F884" t="s">
+        <v>25</v>
+      </c>
+      <c r="G884" t="s">
+        <v>7</v>
+      </c>
+      <c r="H884" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I884">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="885" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A885" t="s">
+        <v>32</v>
+      </c>
+      <c r="B885" t="s">
+        <v>1</v>
+      </c>
+      <c r="C885">
+        <v>10031</v>
+      </c>
+      <c r="D885" t="s">
+        <v>14</v>
+      </c>
+      <c r="E885" t="s">
+        <v>19</v>
+      </c>
+      <c r="F885" t="s">
+        <v>25</v>
+      </c>
+      <c r="G885" t="s">
+        <v>6</v>
+      </c>
+      <c r="H885" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I885">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="886" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A886" t="s">
+        <v>32</v>
+      </c>
+      <c r="B886" t="s">
+        <v>1</v>
+      </c>
+      <c r="C886">
+        <v>10031</v>
+      </c>
+      <c r="D886" t="s">
+        <v>14</v>
+      </c>
+      <c r="E886" t="s">
+        <v>19</v>
+      </c>
+      <c r="F886" t="s">
+        <v>25</v>
+      </c>
+      <c r="G886" t="s">
+        <v>5</v>
+      </c>
+      <c r="H886" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I886">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="887" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A887" t="s">
+        <v>32</v>
+      </c>
+      <c r="B887" t="s">
+        <v>1</v>
+      </c>
+      <c r="C887">
+        <v>10031</v>
+      </c>
+      <c r="D887" t="s">
+        <v>14</v>
+      </c>
+      <c r="E887" t="s">
+        <v>19</v>
+      </c>
+      <c r="F887" t="s">
+        <v>25</v>
+      </c>
+      <c r="G887" t="s">
+        <v>4</v>
+      </c>
+      <c r="H887" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I887">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="888" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A888" t="s">
+        <v>32</v>
+      </c>
+      <c r="B888" t="s">
+        <v>1</v>
+      </c>
+      <c r="C888">
+        <v>10031</v>
+      </c>
+      <c r="D888" t="s">
+        <v>14</v>
+      </c>
+      <c r="E888" t="s">
+        <v>19</v>
+      </c>
+      <c r="F888" t="s">
+        <v>24</v>
+      </c>
+      <c r="G888" t="s">
+        <v>2</v>
+      </c>
+      <c r="H888" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I888">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="889" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A889" t="s">
+        <v>32</v>
+      </c>
+      <c r="B889" t="s">
+        <v>1</v>
+      </c>
+      <c r="C889">
+        <v>10031</v>
+      </c>
+      <c r="D889" t="s">
+        <v>14</v>
+      </c>
+      <c r="E889" t="s">
+        <v>19</v>
+      </c>
+      <c r="F889" t="s">
+        <v>24</v>
+      </c>
+      <c r="G889" t="s">
+        <v>3</v>
+      </c>
+      <c r="H889" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I889">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="890" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A890" t="s">
+        <v>32</v>
+      </c>
+      <c r="B890" t="s">
+        <v>1</v>
+      </c>
+      <c r="C890">
+        <v>10031</v>
+      </c>
+      <c r="D890" t="s">
+        <v>14</v>
+      </c>
+      <c r="E890" t="s">
+        <v>19</v>
+      </c>
+      <c r="F890" t="s">
+        <v>24</v>
+      </c>
+      <c r="G890" t="s">
+        <v>8</v>
+      </c>
+      <c r="H890" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I890">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="891" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A891" t="s">
+        <v>32</v>
+      </c>
+      <c r="B891" t="s">
+        <v>1</v>
+      </c>
+      <c r="C891">
+        <v>10031</v>
+      </c>
+      <c r="D891" t="s">
+        <v>14</v>
+      </c>
+      <c r="E891" t="s">
+        <v>19</v>
+      </c>
+      <c r="F891" t="s">
+        <v>24</v>
+      </c>
+      <c r="G891" t="s">
+        <v>9</v>
+      </c>
+      <c r="H891" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I891">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="892" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A892" t="s">
+        <v>32</v>
+      </c>
+      <c r="B892" t="s">
+        <v>1</v>
+      </c>
+      <c r="C892">
+        <v>10031</v>
+      </c>
+      <c r="D892" t="s">
+        <v>14</v>
+      </c>
+      <c r="E892" t="s">
+        <v>19</v>
+      </c>
+      <c r="F892" t="s">
+        <v>24</v>
+      </c>
+      <c r="G892" t="s">
+        <v>10</v>
+      </c>
+      <c r="H892" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I892">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="893" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A893" t="s">
+        <v>32</v>
+      </c>
+      <c r="B893" t="s">
+        <v>1</v>
+      </c>
+      <c r="C893">
+        <v>10031</v>
+      </c>
+      <c r="D893" t="s">
+        <v>14</v>
+      </c>
+      <c r="E893" t="s">
+        <v>19</v>
+      </c>
+      <c r="F893" t="s">
+        <v>24</v>
+      </c>
+      <c r="G893" t="s">
+        <v>11</v>
+      </c>
+      <c r="H893" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I893">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="894" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A894" t="s">
+        <v>32</v>
+      </c>
+      <c r="B894" t="s">
+        <v>1</v>
+      </c>
+      <c r="C894">
+        <v>10031</v>
+      </c>
+      <c r="D894" t="s">
+        <v>14</v>
+      </c>
+      <c r="E894" t="s">
+        <v>19</v>
+      </c>
+      <c r="F894" t="s">
+        <v>24</v>
+      </c>
+      <c r="G894" t="s">
+        <v>12</v>
+      </c>
+      <c r="H894" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I894">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="895" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A895" t="s">
+        <v>32</v>
+      </c>
+      <c r="B895" t="s">
+        <v>1</v>
+      </c>
+      <c r="C895">
+        <v>10031</v>
+      </c>
+      <c r="D895" t="s">
+        <v>14</v>
+      </c>
+      <c r="E895" t="s">
+        <v>19</v>
+      </c>
+      <c r="F895" t="s">
+        <v>25</v>
+      </c>
+      <c r="G895" t="s">
+        <v>13</v>
+      </c>
+      <c r="H895" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I895">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="896" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A896" t="s">
+        <v>32</v>
+      </c>
+      <c r="B896" t="s">
+        <v>1</v>
+      </c>
+      <c r="C896">
+        <v>10031</v>
+      </c>
+      <c r="D896" t="s">
+        <v>14</v>
+      </c>
+      <c r="E896" t="s">
+        <v>19</v>
+      </c>
+      <c r="F896" t="s">
+        <v>25</v>
+      </c>
+      <c r="G896" t="s">
+        <v>7</v>
+      </c>
+      <c r="H896" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I896">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="897" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A897" t="s">
+        <v>32</v>
+      </c>
+      <c r="B897" t="s">
+        <v>1</v>
+      </c>
+      <c r="C897">
+        <v>10031</v>
+      </c>
+      <c r="D897" t="s">
+        <v>14</v>
+      </c>
+      <c r="E897" t="s">
+        <v>19</v>
+      </c>
+      <c r="F897" t="s">
+        <v>25</v>
+      </c>
+      <c r="G897" t="s">
+        <v>6</v>
+      </c>
+      <c r="H897" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I897">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="898" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A898" t="s">
+        <v>32</v>
+      </c>
+      <c r="B898" t="s">
+        <v>1</v>
+      </c>
+      <c r="C898">
+        <v>10031</v>
+      </c>
+      <c r="D898" t="s">
+        <v>14</v>
+      </c>
+      <c r="E898" t="s">
+        <v>19</v>
+      </c>
+      <c r="F898" t="s">
+        <v>25</v>
+      </c>
+      <c r="G898" t="s">
+        <v>5</v>
+      </c>
+      <c r="H898" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I898">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="899" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A899" t="s">
+        <v>32</v>
+      </c>
+      <c r="B899" t="s">
+        <v>1</v>
+      </c>
+      <c r="C899">
+        <v>10031</v>
+      </c>
+      <c r="D899" t="s">
+        <v>14</v>
+      </c>
+      <c r="E899" t="s">
+        <v>19</v>
+      </c>
+      <c r="F899" t="s">
+        <v>25</v>
+      </c>
+      <c r="G899" t="s">
+        <v>4</v>
+      </c>
+      <c r="H899" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I899">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I875" xr:uid="{0DC7CFB6-8D2D-48BC-8422-B9E5DAEAAFDA}"/>
+  <autoFilter ref="A1:I875" xr:uid="{0DC7CFB6-8D2D-48BC-8422-B9E5DAEAAFDA}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="10031"/>
+        <filter val="10201"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="COMML"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="PLUMBING"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
